--- a/cms/app/content/faceswap-content.xlsx
+++ b/cms/app/content/faceswap-content.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shawaiz/git/pixel-morph/cms/app/content/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A97F3C8-104C-574C-98C2-C60F71C51858}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA352B7F-958C-FC4C-A947-A2842422D6AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25600" windowHeight="13720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2613" uniqueCount="1656">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2614" uniqueCount="1657">
   <si>
     <t>Overview</t>
   </si>
@@ -5617,6 +5617,9 @@
   </si>
   <si>
     <t>Отзывы пользователей</t>
+  </si>
+  <si>
+    <t>Бесплатный обмен лицами AI - лучший обменник лиц онлайн</t>
   </si>
 </sst>
 </file>
@@ -6078,29 +6081,29 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6404,13 +6407,13 @@
       <c r="K2" s="8"/>
       <c r="L2" s="8"/>
       <c r="M2" s="8"/>
-      <c r="N2" s="76"/>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
+      <c r="N2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
       <c r="Q2" s="8"/>
       <c r="R2" s="8"/>
-      <c r="S2" s="76"/>
-      <c r="T2" s="77"/>
+      <c r="S2" s="77"/>
+      <c r="T2" s="78"/>
     </row>
     <row r="3" spans="1:20" ht="15.75" customHeight="1">
       <c r="A3" s="49" t="s">
@@ -6442,13 +6445,13 @@
       <c r="K3" s="7"/>
       <c r="L3" s="7"/>
       <c r="M3" s="8"/>
-      <c r="N3" s="76"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
+      <c r="N3" s="77"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
       <c r="Q3" s="8"/>
       <c r="R3" s="8"/>
-      <c r="S3" s="76"/>
-      <c r="T3" s="77"/>
+      <c r="S3" s="77"/>
+      <c r="T3" s="78"/>
     </row>
     <row r="4" spans="1:20" ht="15.75" customHeight="1">
       <c r="A4" s="54" t="s">
@@ -6505,15 +6508,15 @@
       <c r="L5" s="8"/>
       <c r="M5" s="8"/>
       <c r="N5" s="8"/>
-      <c r="O5" s="76"/>
-      <c r="P5" s="77"/>
+      <c r="O5" s="77"/>
+      <c r="P5" s="78"/>
       <c r="Q5" s="8"/>
       <c r="R5" s="8"/>
-      <c r="S5" s="76"/>
-      <c r="T5" s="77"/>
+      <c r="S5" s="77"/>
+      <c r="T5" s="78"/>
     </row>
     <row r="6" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A6" s="79" t="s">
+      <c r="A6" s="85" t="s">
         <v>30</v>
       </c>
       <c r="B6" s="59" t="s">
@@ -6544,16 +6547,16 @@
       <c r="K6" s="8"/>
       <c r="L6" s="8"/>
       <c r="M6" s="8"/>
-      <c r="N6" s="76"/>
-      <c r="O6" s="77"/>
-      <c r="P6" s="77"/>
+      <c r="N6" s="77"/>
+      <c r="O6" s="78"/>
+      <c r="P6" s="78"/>
       <c r="Q6" s="8"/>
       <c r="R6" s="8"/>
-      <c r="S6" s="76"/>
-      <c r="T6" s="77"/>
+      <c r="S6" s="77"/>
+      <c r="T6" s="78"/>
     </row>
     <row r="7" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A7" s="80"/>
+      <c r="A7" s="82"/>
       <c r="B7" s="61" t="s">
         <v>35</v>
       </c>
@@ -6569,17 +6572,17 @@
       <c r="J7" s="8"/>
       <c r="K7" s="8"/>
       <c r="L7" s="8"/>
-      <c r="M7" s="76"/>
-      <c r="N7" s="77"/>
+      <c r="M7" s="77"/>
+      <c r="N7" s="78"/>
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
-      <c r="R7" s="76"/>
-      <c r="S7" s="77"/>
+      <c r="R7" s="77"/>
+      <c r="S7" s="78"/>
       <c r="T7" s="8"/>
     </row>
     <row r="8" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A8" s="80"/>
+      <c r="A8" s="82"/>
       <c r="B8" s="61" t="s">
         <v>31</v>
       </c>
@@ -6607,17 +6610,17 @@
       <c r="J8" s="8"/>
       <c r="K8" s="8"/>
       <c r="L8" s="8"/>
-      <c r="M8" s="76"/>
-      <c r="N8" s="77"/>
-      <c r="O8" s="77"/>
+      <c r="M8" s="77"/>
+      <c r="N8" s="78"/>
+      <c r="O8" s="78"/>
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
-      <c r="R8" s="76"/>
-      <c r="S8" s="77"/>
-      <c r="T8" s="77"/>
+      <c r="R8" s="77"/>
+      <c r="S8" s="78"/>
+      <c r="T8" s="78"/>
     </row>
     <row r="9" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A9" s="80"/>
+      <c r="A9" s="82"/>
       <c r="B9" s="61" t="s">
         <v>35</v>
       </c>
@@ -6633,17 +6636,17 @@
       <c r="J9" s="8"/>
       <c r="K9" s="8"/>
       <c r="L9" s="8"/>
-      <c r="M9" s="76"/>
-      <c r="N9" s="77"/>
+      <c r="M9" s="77"/>
+      <c r="N9" s="78"/>
       <c r="O9" s="8"/>
       <c r="P9" s="8"/>
       <c r="Q9" s="8"/>
-      <c r="R9" s="76"/>
-      <c r="S9" s="77"/>
+      <c r="R9" s="77"/>
+      <c r="S9" s="78"/>
       <c r="T9" s="8"/>
     </row>
     <row r="10" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A10" s="80"/>
+      <c r="A10" s="82"/>
       <c r="B10" s="61" t="s">
         <v>31</v>
       </c>
@@ -6671,17 +6674,17 @@
       <c r="J10" s="8"/>
       <c r="K10" s="8"/>
       <c r="L10" s="8"/>
-      <c r="M10" s="76"/>
-      <c r="N10" s="77"/>
-      <c r="O10" s="77"/>
+      <c r="M10" s="77"/>
+      <c r="N10" s="78"/>
+      <c r="O10" s="78"/>
       <c r="P10" s="8"/>
       <c r="Q10" s="8"/>
-      <c r="R10" s="76"/>
-      <c r="S10" s="77"/>
-      <c r="T10" s="77"/>
+      <c r="R10" s="77"/>
+      <c r="S10" s="78"/>
+      <c r="T10" s="78"/>
     </row>
     <row r="11" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A11" s="80"/>
+      <c r="A11" s="82"/>
       <c r="B11" s="61" t="s">
         <v>40</v>
       </c>
@@ -6709,17 +6712,17 @@
       <c r="J11" s="8"/>
       <c r="K11" s="8"/>
       <c r="L11" s="8"/>
-      <c r="M11" s="76"/>
-      <c r="N11" s="77"/>
-      <c r="O11" s="77"/>
+      <c r="M11" s="77"/>
+      <c r="N11" s="78"/>
+      <c r="O11" s="78"/>
       <c r="P11" s="8"/>
       <c r="Q11" s="8"/>
-      <c r="R11" s="76"/>
-      <c r="S11" s="77"/>
-      <c r="T11" s="77"/>
+      <c r="R11" s="77"/>
+      <c r="S11" s="78"/>
+      <c r="T11" s="78"/>
     </row>
     <row r="12" spans="1:20" ht="28">
-      <c r="A12" s="80"/>
+      <c r="A12" s="82"/>
       <c r="B12" s="61" t="s">
         <v>45</v>
       </c>
@@ -6735,14 +6738,14 @@
       <c r="J12" s="8"/>
       <c r="K12" s="8"/>
       <c r="L12" s="18"/>
-      <c r="M12" s="82"/>
-      <c r="N12" s="77"/>
-      <c r="O12" s="77"/>
+      <c r="M12" s="80"/>
+      <c r="N12" s="78"/>
+      <c r="O12" s="78"/>
       <c r="P12" s="18"/>
       <c r="Q12" s="18"/>
-      <c r="R12" s="82"/>
-      <c r="S12" s="77"/>
-      <c r="T12" s="77"/>
+      <c r="R12" s="80"/>
+      <c r="S12" s="78"/>
+      <c r="T12" s="78"/>
     </row>
     <row r="13" spans="1:20" ht="15.75" customHeight="1">
       <c r="A13" s="59" t="s">
@@ -6776,13 +6779,13 @@
       <c r="K13" s="8"/>
       <c r="L13" s="8"/>
       <c r="M13" s="8"/>
-      <c r="N13" s="76"/>
-      <c r="O13" s="77"/>
-      <c r="P13" s="77"/>
+      <c r="N13" s="77"/>
+      <c r="O13" s="78"/>
+      <c r="P13" s="78"/>
       <c r="Q13" s="8"/>
       <c r="R13" s="8"/>
-      <c r="S13" s="76"/>
-      <c r="T13" s="77"/>
+      <c r="S13" s="77"/>
+      <c r="T13" s="78"/>
     </row>
     <row r="14" spans="1:20" ht="15.75" customHeight="1">
       <c r="A14" s="61" t="s">
@@ -6816,13 +6819,13 @@
       <c r="K14" s="7"/>
       <c r="L14" s="7"/>
       <c r="M14" s="8"/>
-      <c r="N14" s="76"/>
-      <c r="O14" s="77"/>
-      <c r="P14" s="77"/>
+      <c r="N14" s="77"/>
+      <c r="O14" s="78"/>
+      <c r="P14" s="78"/>
       <c r="Q14" s="8"/>
       <c r="R14" s="8"/>
-      <c r="S14" s="76"/>
-      <c r="T14" s="77"/>
+      <c r="S14" s="77"/>
+      <c r="T14" s="78"/>
     </row>
     <row r="15" spans="1:20" ht="15.75" customHeight="1">
       <c r="A15" s="61" t="s">
@@ -6844,13 +6847,13 @@
       <c r="K15" s="8"/>
       <c r="L15" s="8"/>
       <c r="M15" s="8"/>
-      <c r="N15" s="76"/>
-      <c r="O15" s="77"/>
+      <c r="N15" s="77"/>
+      <c r="O15" s="78"/>
       <c r="P15" s="8"/>
       <c r="Q15" s="8"/>
       <c r="R15" s="8"/>
-      <c r="S15" s="76"/>
-      <c r="T15" s="77"/>
+      <c r="S15" s="77"/>
+      <c r="T15" s="78"/>
     </row>
     <row r="16" spans="1:20" ht="15.75" customHeight="1">
       <c r="A16" s="61" t="s">
@@ -6884,13 +6887,13 @@
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
       <c r="M16" s="8"/>
-      <c r="N16" s="76"/>
-      <c r="O16" s="77"/>
+      <c r="N16" s="77"/>
+      <c r="O16" s="78"/>
       <c r="P16" s="8"/>
       <c r="Q16" s="8"/>
       <c r="R16" s="8"/>
-      <c r="S16" s="76"/>
-      <c r="T16" s="77"/>
+      <c r="S16" s="77"/>
+      <c r="T16" s="78"/>
     </row>
     <row r="17" spans="1:20" ht="28">
       <c r="A17" s="61" t="s">
@@ -6912,13 +6915,13 @@
       <c r="K17" s="8"/>
       <c r="L17" s="8"/>
       <c r="M17" s="18"/>
-      <c r="N17" s="82"/>
-      <c r="O17" s="77"/>
-      <c r="P17" s="77"/>
+      <c r="N17" s="80"/>
+      <c r="O17" s="78"/>
+      <c r="P17" s="78"/>
       <c r="Q17" s="18"/>
       <c r="R17" s="18"/>
-      <c r="S17" s="82"/>
-      <c r="T17" s="77"/>
+      <c r="S17" s="80"/>
+      <c r="T17" s="78"/>
     </row>
     <row r="18" spans="1:20" ht="15.75" customHeight="1">
       <c r="A18" s="61" t="s">
@@ -6952,13 +6955,13 @@
       <c r="K18" s="8"/>
       <c r="L18" s="8"/>
       <c r="M18" s="8"/>
-      <c r="N18" s="76"/>
-      <c r="O18" s="77"/>
-      <c r="P18" s="77"/>
+      <c r="N18" s="77"/>
+      <c r="O18" s="78"/>
+      <c r="P18" s="78"/>
       <c r="Q18" s="8"/>
       <c r="R18" s="8"/>
-      <c r="S18" s="76"/>
-      <c r="T18" s="77"/>
+      <c r="S18" s="77"/>
+      <c r="T18" s="78"/>
     </row>
     <row r="19" spans="1:20" ht="15.75" customHeight="1">
       <c r="A19" s="61" t="s">
@@ -6992,13 +6995,13 @@
       <c r="K19" s="7"/>
       <c r="L19" s="7"/>
       <c r="M19" s="8"/>
-      <c r="N19" s="76"/>
-      <c r="O19" s="77"/>
-      <c r="P19" s="77"/>
+      <c r="N19" s="77"/>
+      <c r="O19" s="78"/>
+      <c r="P19" s="78"/>
       <c r="Q19" s="8"/>
       <c r="R19" s="8"/>
-      <c r="S19" s="76"/>
-      <c r="T19" s="77"/>
+      <c r="S19" s="77"/>
+      <c r="T19" s="78"/>
     </row>
     <row r="20" spans="1:20" ht="15.75" customHeight="1">
       <c r="A20" s="49" t="s">
@@ -7053,7 +7056,9 @@
       <c r="D21" s="62" t="s">
         <v>73</v>
       </c>
-      <c r="E21" s="66"/>
+      <c r="E21" s="66" t="s">
+        <v>1656</v>
+      </c>
       <c r="F21" s="58" t="s">
         <v>74</v>
       </c>
@@ -7070,16 +7075,16 @@
       <c r="K21" s="8"/>
       <c r="L21" s="8"/>
       <c r="M21" s="4"/>
-      <c r="N21" s="78"/>
-      <c r="O21" s="77"/>
-      <c r="P21" s="77"/>
+      <c r="N21" s="79"/>
+      <c r="O21" s="78"/>
+      <c r="P21" s="78"/>
       <c r="Q21" s="4"/>
       <c r="R21" s="4"/>
-      <c r="S21" s="78"/>
-      <c r="T21" s="77"/>
+      <c r="S21" s="79"/>
+      <c r="T21" s="78"/>
     </row>
     <row r="22" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A22" s="80"/>
+      <c r="A22" s="82"/>
       <c r="B22" s="50"/>
       <c r="C22" s="49" t="s">
         <v>78</v>
@@ -7105,14 +7110,14 @@
       <c r="J22" s="8"/>
       <c r="K22" s="8"/>
       <c r="L22" s="8"/>
-      <c r="M22" s="76"/>
-      <c r="N22" s="77"/>
-      <c r="O22" s="77"/>
+      <c r="M22" s="77"/>
+      <c r="N22" s="78"/>
+      <c r="O22" s="78"/>
       <c r="P22" s="8"/>
       <c r="Q22" s="8"/>
-      <c r="R22" s="76"/>
-      <c r="S22" s="77"/>
-      <c r="T22" s="77"/>
+      <c r="R22" s="77"/>
+      <c r="S22" s="78"/>
+      <c r="T22" s="78"/>
     </row>
     <row r="23" spans="1:20" ht="15.75" customHeight="1">
       <c r="A23" s="81" t="s">
@@ -7146,16 +7151,16 @@
       <c r="K23" s="8"/>
       <c r="L23" s="8"/>
       <c r="M23" s="4"/>
-      <c r="N23" s="78"/>
-      <c r="O23" s="77"/>
-      <c r="P23" s="77"/>
+      <c r="N23" s="79"/>
+      <c r="O23" s="78"/>
+      <c r="P23" s="78"/>
       <c r="Q23" s="4"/>
       <c r="R23" s="4"/>
-      <c r="S23" s="78"/>
-      <c r="T23" s="77"/>
+      <c r="S23" s="79"/>
+      <c r="T23" s="78"/>
     </row>
     <row r="24" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A24" s="80"/>
+      <c r="A24" s="82"/>
       <c r="B24" s="49" t="s">
         <v>92</v>
       </c>
@@ -7183,17 +7188,17 @@
       <c r="J24" s="8"/>
       <c r="K24" s="8"/>
       <c r="L24" s="4"/>
-      <c r="M24" s="78"/>
-      <c r="N24" s="77"/>
-      <c r="O24" s="77"/>
+      <c r="M24" s="79"/>
+      <c r="N24" s="78"/>
+      <c r="O24" s="78"/>
       <c r="P24" s="4"/>
       <c r="Q24" s="4"/>
-      <c r="R24" s="78"/>
-      <c r="S24" s="77"/>
-      <c r="T24" s="77"/>
+      <c r="R24" s="79"/>
+      <c r="S24" s="78"/>
+      <c r="T24" s="78"/>
     </row>
     <row r="25" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A25" s="80"/>
+      <c r="A25" s="82"/>
       <c r="B25" s="50"/>
       <c r="C25" s="49" t="s">
         <v>99</v>
@@ -7219,17 +7224,17 @@
       <c r="J25" s="8"/>
       <c r="K25" s="8"/>
       <c r="L25" s="8"/>
-      <c r="M25" s="76"/>
-      <c r="N25" s="77"/>
-      <c r="O25" s="77"/>
+      <c r="M25" s="77"/>
+      <c r="N25" s="78"/>
+      <c r="O25" s="78"/>
       <c r="P25" s="8"/>
       <c r="Q25" s="8"/>
-      <c r="R25" s="76"/>
-      <c r="S25" s="77"/>
-      <c r="T25" s="77"/>
+      <c r="R25" s="77"/>
+      <c r="S25" s="78"/>
+      <c r="T25" s="78"/>
     </row>
     <row r="26" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A26" s="80"/>
+      <c r="A26" s="82"/>
       <c r="B26" s="49" t="s">
         <v>92</v>
       </c>
@@ -7257,17 +7262,17 @@
       <c r="J26" s="8"/>
       <c r="K26" s="8"/>
       <c r="L26" s="4"/>
-      <c r="M26" s="78"/>
-      <c r="N26" s="77"/>
-      <c r="O26" s="77"/>
+      <c r="M26" s="79"/>
+      <c r="N26" s="78"/>
+      <c r="O26" s="78"/>
       <c r="P26" s="4"/>
       <c r="Q26" s="4"/>
-      <c r="R26" s="78"/>
-      <c r="S26" s="77"/>
-      <c r="T26" s="77"/>
+      <c r="R26" s="79"/>
+      <c r="S26" s="78"/>
+      <c r="T26" s="78"/>
     </row>
     <row r="27" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A27" s="80"/>
+      <c r="A27" s="82"/>
       <c r="B27" s="50"/>
       <c r="C27" s="49" t="s">
         <v>111</v>
@@ -7293,17 +7298,17 @@
       <c r="J27" s="8"/>
       <c r="K27" s="8"/>
       <c r="L27" s="8"/>
-      <c r="M27" s="76"/>
-      <c r="N27" s="77"/>
-      <c r="O27" s="77"/>
+      <c r="M27" s="77"/>
+      <c r="N27" s="78"/>
+      <c r="O27" s="78"/>
       <c r="P27" s="8"/>
       <c r="Q27" s="8"/>
-      <c r="R27" s="76"/>
-      <c r="S27" s="77"/>
-      <c r="T27" s="77"/>
+      <c r="R27" s="77"/>
+      <c r="S27" s="78"/>
+      <c r="T27" s="78"/>
     </row>
     <row r="28" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A28" s="80"/>
+      <c r="A28" s="82"/>
       <c r="B28" s="49" t="s">
         <v>92</v>
       </c>
@@ -7331,17 +7336,17 @@
       <c r="J28" s="8"/>
       <c r="K28" s="8"/>
       <c r="L28" s="4"/>
-      <c r="M28" s="78"/>
-      <c r="N28" s="77"/>
-      <c r="O28" s="77"/>
+      <c r="M28" s="79"/>
+      <c r="N28" s="78"/>
+      <c r="O28" s="78"/>
       <c r="P28" s="4"/>
       <c r="Q28" s="4"/>
-      <c r="R28" s="78"/>
-      <c r="S28" s="77"/>
-      <c r="T28" s="77"/>
+      <c r="R28" s="79"/>
+      <c r="S28" s="78"/>
+      <c r="T28" s="78"/>
     </row>
     <row r="29" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A29" s="80"/>
+      <c r="A29" s="82"/>
       <c r="B29" s="50"/>
       <c r="C29" s="49" t="s">
         <v>123</v>
@@ -7367,17 +7372,17 @@
       <c r="J29" s="8"/>
       <c r="K29" s="8"/>
       <c r="L29" s="8"/>
-      <c r="M29" s="76"/>
-      <c r="N29" s="77"/>
-      <c r="O29" s="77"/>
+      <c r="M29" s="77"/>
+      <c r="N29" s="78"/>
+      <c r="O29" s="78"/>
       <c r="P29" s="8"/>
       <c r="Q29" s="8"/>
-      <c r="R29" s="76"/>
-      <c r="S29" s="77"/>
-      <c r="T29" s="77"/>
+      <c r="R29" s="77"/>
+      <c r="S29" s="78"/>
+      <c r="T29" s="78"/>
     </row>
     <row r="30" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A30" s="80"/>
+      <c r="A30" s="82"/>
       <c r="B30" s="49" t="s">
         <v>92</v>
       </c>
@@ -7405,17 +7410,17 @@
       <c r="J30" s="8"/>
       <c r="K30" s="8"/>
       <c r="L30" s="4"/>
-      <c r="M30" s="78"/>
-      <c r="N30" s="77"/>
-      <c r="O30" s="77"/>
+      <c r="M30" s="79"/>
+      <c r="N30" s="78"/>
+      <c r="O30" s="78"/>
       <c r="P30" s="4"/>
       <c r="Q30" s="4"/>
-      <c r="R30" s="78"/>
-      <c r="S30" s="77"/>
-      <c r="T30" s="77"/>
+      <c r="R30" s="79"/>
+      <c r="S30" s="78"/>
+      <c r="T30" s="78"/>
     </row>
     <row r="31" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A31" s="80"/>
+      <c r="A31" s="82"/>
       <c r="B31" s="50"/>
       <c r="C31" s="49" t="s">
         <v>135</v>
@@ -7441,14 +7446,14 @@
       <c r="J31" s="8"/>
       <c r="K31" s="8"/>
       <c r="L31" s="8"/>
-      <c r="M31" s="76"/>
-      <c r="N31" s="77"/>
-      <c r="O31" s="77"/>
+      <c r="M31" s="77"/>
+      <c r="N31" s="78"/>
+      <c r="O31" s="78"/>
       <c r="P31" s="8"/>
       <c r="Q31" s="8"/>
-      <c r="R31" s="76"/>
-      <c r="S31" s="77"/>
-      <c r="T31" s="77"/>
+      <c r="R31" s="77"/>
+      <c r="S31" s="78"/>
+      <c r="T31" s="78"/>
     </row>
     <row r="32" spans="1:20" ht="15.75" customHeight="1">
       <c r="A32" s="81" t="s">
@@ -7482,16 +7487,16 @@
       <c r="K32" s="8"/>
       <c r="L32" s="8"/>
       <c r="M32" s="4"/>
-      <c r="N32" s="78"/>
-      <c r="O32" s="77"/>
-      <c r="P32" s="77"/>
+      <c r="N32" s="79"/>
+      <c r="O32" s="78"/>
+      <c r="P32" s="78"/>
       <c r="Q32" s="4"/>
       <c r="R32" s="4"/>
-      <c r="S32" s="78"/>
-      <c r="T32" s="77"/>
+      <c r="S32" s="79"/>
+      <c r="T32" s="78"/>
     </row>
     <row r="33" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A33" s="80"/>
+      <c r="A33" s="82"/>
       <c r="B33" s="50"/>
       <c r="C33" s="49" t="s">
         <v>148</v>
@@ -7517,17 +7522,17 @@
       <c r="J33" s="8"/>
       <c r="K33" s="8"/>
       <c r="L33" s="8"/>
-      <c r="M33" s="76"/>
-      <c r="N33" s="77"/>
-      <c r="O33" s="77"/>
+      <c r="M33" s="77"/>
+      <c r="N33" s="78"/>
+      <c r="O33" s="78"/>
       <c r="P33" s="8"/>
       <c r="Q33" s="8"/>
-      <c r="R33" s="76"/>
-      <c r="S33" s="77"/>
-      <c r="T33" s="77"/>
+      <c r="R33" s="77"/>
+      <c r="S33" s="78"/>
+      <c r="T33" s="78"/>
     </row>
     <row r="34" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A34" s="80"/>
+      <c r="A34" s="82"/>
       <c r="B34" s="49" t="s">
         <v>92</v>
       </c>
@@ -7555,17 +7560,17 @@
       <c r="J34" s="8"/>
       <c r="K34" s="8"/>
       <c r="L34" s="4"/>
-      <c r="M34" s="78"/>
-      <c r="N34" s="77"/>
-      <c r="O34" s="77"/>
+      <c r="M34" s="79"/>
+      <c r="N34" s="78"/>
+      <c r="O34" s="78"/>
       <c r="P34" s="4"/>
       <c r="Q34" s="4"/>
-      <c r="R34" s="78"/>
-      <c r="S34" s="77"/>
-      <c r="T34" s="77"/>
+      <c r="R34" s="79"/>
+      <c r="S34" s="78"/>
+      <c r="T34" s="78"/>
     </row>
     <row r="35" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A35" s="80"/>
+      <c r="A35" s="82"/>
       <c r="B35" s="50"/>
       <c r="C35" s="49" t="s">
         <v>160</v>
@@ -7591,17 +7596,17 @@
       <c r="J35" s="8"/>
       <c r="K35" s="8"/>
       <c r="L35" s="8"/>
-      <c r="M35" s="76"/>
-      <c r="N35" s="77"/>
-      <c r="O35" s="77"/>
+      <c r="M35" s="77"/>
+      <c r="N35" s="78"/>
+      <c r="O35" s="78"/>
       <c r="P35" s="8"/>
       <c r="Q35" s="8"/>
-      <c r="R35" s="76"/>
-      <c r="S35" s="77"/>
-      <c r="T35" s="77"/>
+      <c r="R35" s="77"/>
+      <c r="S35" s="78"/>
+      <c r="T35" s="78"/>
     </row>
     <row r="36" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A36" s="80"/>
+      <c r="A36" s="82"/>
       <c r="B36" s="49" t="s">
         <v>92</v>
       </c>
@@ -7629,17 +7634,17 @@
       <c r="J36" s="8"/>
       <c r="K36" s="8"/>
       <c r="L36" s="4"/>
-      <c r="M36" s="78"/>
-      <c r="N36" s="77"/>
-      <c r="O36" s="77"/>
+      <c r="M36" s="79"/>
+      <c r="N36" s="78"/>
+      <c r="O36" s="78"/>
       <c r="P36" s="4"/>
       <c r="Q36" s="4"/>
-      <c r="R36" s="78"/>
-      <c r="S36" s="77"/>
-      <c r="T36" s="77"/>
+      <c r="R36" s="79"/>
+      <c r="S36" s="78"/>
+      <c r="T36" s="78"/>
     </row>
     <row r="37" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A37" s="80"/>
+      <c r="A37" s="82"/>
       <c r="B37" s="50"/>
       <c r="C37" s="49" t="s">
         <v>172</v>
@@ -7665,17 +7670,17 @@
       <c r="J37" s="8"/>
       <c r="K37" s="8"/>
       <c r="L37" s="8"/>
-      <c r="M37" s="76"/>
-      <c r="N37" s="77"/>
-      <c r="O37" s="77"/>
+      <c r="M37" s="77"/>
+      <c r="N37" s="78"/>
+      <c r="O37" s="78"/>
       <c r="P37" s="8"/>
       <c r="Q37" s="8"/>
-      <c r="R37" s="76"/>
-      <c r="S37" s="77"/>
-      <c r="T37" s="77"/>
+      <c r="R37" s="77"/>
+      <c r="S37" s="78"/>
+      <c r="T37" s="78"/>
     </row>
     <row r="38" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A38" s="80"/>
+      <c r="A38" s="82"/>
       <c r="B38" s="49" t="s">
         <v>92</v>
       </c>
@@ -7703,17 +7708,17 @@
       <c r="J38" s="8"/>
       <c r="K38" s="8"/>
       <c r="L38" s="4"/>
-      <c r="M38" s="78"/>
-      <c r="N38" s="77"/>
-      <c r="O38" s="77"/>
+      <c r="M38" s="79"/>
+      <c r="N38" s="78"/>
+      <c r="O38" s="78"/>
       <c r="P38" s="4"/>
       <c r="Q38" s="4"/>
-      <c r="R38" s="78"/>
-      <c r="S38" s="77"/>
-      <c r="T38" s="77"/>
+      <c r="R38" s="79"/>
+      <c r="S38" s="78"/>
+      <c r="T38" s="78"/>
     </row>
     <row r="39" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A39" s="80"/>
+      <c r="A39" s="82"/>
       <c r="B39" s="50"/>
       <c r="C39" s="49" t="s">
         <v>184</v>
@@ -7739,17 +7744,17 @@
       <c r="J39" s="8"/>
       <c r="K39" s="8"/>
       <c r="L39" s="8"/>
-      <c r="M39" s="76"/>
-      <c r="N39" s="77"/>
-      <c r="O39" s="77"/>
+      <c r="M39" s="77"/>
+      <c r="N39" s="78"/>
+      <c r="O39" s="78"/>
       <c r="P39" s="8"/>
       <c r="Q39" s="8"/>
-      <c r="R39" s="76"/>
-      <c r="S39" s="77"/>
-      <c r="T39" s="77"/>
+      <c r="R39" s="77"/>
+      <c r="S39" s="78"/>
+      <c r="T39" s="78"/>
     </row>
     <row r="40" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A40" s="80"/>
+      <c r="A40" s="82"/>
       <c r="B40" s="49" t="s">
         <v>92</v>
       </c>
@@ -7777,17 +7782,17 @@
       <c r="J40" s="8"/>
       <c r="K40" s="8"/>
       <c r="L40" s="4"/>
-      <c r="M40" s="78"/>
-      <c r="N40" s="77"/>
-      <c r="O40" s="77"/>
+      <c r="M40" s="79"/>
+      <c r="N40" s="78"/>
+      <c r="O40" s="78"/>
       <c r="P40" s="4"/>
       <c r="Q40" s="4"/>
-      <c r="R40" s="78"/>
-      <c r="S40" s="77"/>
-      <c r="T40" s="77"/>
+      <c r="R40" s="79"/>
+      <c r="S40" s="78"/>
+      <c r="T40" s="78"/>
     </row>
     <row r="41" spans="1:20" ht="182">
-      <c r="A41" s="80"/>
+      <c r="A41" s="82"/>
       <c r="B41" s="50"/>
       <c r="C41" s="49" t="s">
         <v>196</v>
@@ -7813,14 +7818,14 @@
       <c r="J41" s="8"/>
       <c r="K41" s="8"/>
       <c r="L41" s="8"/>
-      <c r="M41" s="76"/>
-      <c r="N41" s="77"/>
-      <c r="O41" s="77"/>
+      <c r="M41" s="77"/>
+      <c r="N41" s="78"/>
+      <c r="O41" s="78"/>
       <c r="P41" s="8"/>
       <c r="Q41" s="8"/>
-      <c r="R41" s="76"/>
-      <c r="S41" s="77"/>
-      <c r="T41" s="77"/>
+      <c r="R41" s="77"/>
+      <c r="S41" s="78"/>
+      <c r="T41" s="78"/>
     </row>
     <row r="42" spans="1:20" ht="28">
       <c r="A42" s="81" t="s">
@@ -7854,16 +7859,16 @@
       <c r="K42" s="8"/>
       <c r="L42" s="8"/>
       <c r="M42" s="4"/>
-      <c r="N42" s="78"/>
-      <c r="O42" s="77"/>
-      <c r="P42" s="77"/>
+      <c r="N42" s="79"/>
+      <c r="O42" s="78"/>
+      <c r="P42" s="78"/>
       <c r="Q42" s="4"/>
       <c r="R42" s="4"/>
-      <c r="S42" s="78"/>
-      <c r="T42" s="77"/>
+      <c r="S42" s="79"/>
+      <c r="T42" s="78"/>
     </row>
     <row r="43" spans="1:20" ht="14">
-      <c r="A43" s="80"/>
+      <c r="A43" s="82"/>
       <c r="B43" s="50"/>
       <c r="C43" s="49" t="s">
         <v>209</v>
@@ -7889,17 +7894,17 @@
       <c r="J43" s="8"/>
       <c r="K43" s="8"/>
       <c r="L43" s="4"/>
-      <c r="M43" s="78"/>
-      <c r="N43" s="77"/>
+      <c r="M43" s="79"/>
+      <c r="N43" s="78"/>
       <c r="O43" s="8"/>
       <c r="P43" s="4"/>
       <c r="Q43" s="4"/>
-      <c r="R43" s="78"/>
-      <c r="S43" s="77"/>
-      <c r="T43" s="77"/>
+      <c r="R43" s="79"/>
+      <c r="S43" s="78"/>
+      <c r="T43" s="78"/>
     </row>
     <row r="44" spans="1:20" ht="28">
-      <c r="A44" s="80"/>
+      <c r="A44" s="82"/>
       <c r="B44" s="50"/>
       <c r="C44" s="49" t="s">
         <v>215</v>
@@ -7925,17 +7930,17 @@
       <c r="J44" s="8"/>
       <c r="K44" s="8"/>
       <c r="L44" s="8"/>
-      <c r="M44" s="76"/>
-      <c r="N44" s="77"/>
-      <c r="O44" s="77"/>
+      <c r="M44" s="77"/>
+      <c r="N44" s="78"/>
+      <c r="O44" s="78"/>
       <c r="P44" s="8"/>
       <c r="Q44" s="8"/>
-      <c r="R44" s="76"/>
-      <c r="S44" s="77"/>
-      <c r="T44" s="77"/>
+      <c r="R44" s="77"/>
+      <c r="S44" s="78"/>
+      <c r="T44" s="78"/>
     </row>
     <row r="45" spans="1:20" ht="14">
-      <c r="A45" s="80"/>
+      <c r="A45" s="82"/>
       <c r="B45" s="50"/>
       <c r="C45" s="49" t="s">
         <v>221</v>
@@ -7961,17 +7966,17 @@
       <c r="J45" s="8"/>
       <c r="K45" s="8"/>
       <c r="L45" s="4"/>
-      <c r="M45" s="78"/>
-      <c r="N45" s="77"/>
-      <c r="O45" s="77"/>
+      <c r="M45" s="79"/>
+      <c r="N45" s="78"/>
+      <c r="O45" s="78"/>
       <c r="P45" s="4"/>
       <c r="Q45" s="4"/>
-      <c r="R45" s="78"/>
-      <c r="S45" s="77"/>
-      <c r="T45" s="77"/>
+      <c r="R45" s="79"/>
+      <c r="S45" s="78"/>
+      <c r="T45" s="78"/>
     </row>
     <row r="46" spans="1:20" ht="42">
-      <c r="A46" s="80"/>
+      <c r="A46" s="82"/>
       <c r="B46" s="50"/>
       <c r="C46" s="49" t="s">
         <v>222</v>
@@ -7997,17 +8002,17 @@
       <c r="J46" s="8"/>
       <c r="K46" s="8"/>
       <c r="L46" s="8"/>
-      <c r="M46" s="76"/>
-      <c r="N46" s="77"/>
-      <c r="O46" s="77"/>
+      <c r="M46" s="77"/>
+      <c r="N46" s="78"/>
+      <c r="O46" s="78"/>
       <c r="P46" s="8"/>
       <c r="Q46" s="8"/>
-      <c r="R46" s="76"/>
-      <c r="S46" s="77"/>
-      <c r="T46" s="77"/>
+      <c r="R46" s="77"/>
+      <c r="S46" s="78"/>
+      <c r="T46" s="78"/>
     </row>
     <row r="47" spans="1:20" ht="14">
-      <c r="A47" s="80"/>
+      <c r="A47" s="82"/>
       <c r="B47" s="50"/>
       <c r="C47" s="49" t="s">
         <v>228</v>
@@ -8033,17 +8038,17 @@
       <c r="J47" s="8"/>
       <c r="K47" s="8"/>
       <c r="L47" s="4"/>
-      <c r="M47" s="78"/>
-      <c r="N47" s="77"/>
-      <c r="O47" s="77"/>
+      <c r="M47" s="79"/>
+      <c r="N47" s="78"/>
+      <c r="O47" s="78"/>
       <c r="P47" s="4"/>
       <c r="Q47" s="4"/>
-      <c r="R47" s="78"/>
-      <c r="S47" s="77"/>
+      <c r="R47" s="79"/>
+      <c r="S47" s="78"/>
       <c r="T47" s="8"/>
     </row>
     <row r="48" spans="1:20" ht="13">
-      <c r="A48" s="80"/>
+      <c r="A48" s="82"/>
       <c r="B48" s="50"/>
       <c r="C48" s="49"/>
       <c r="D48" s="62"/>
@@ -8062,7 +8067,7 @@
       <c r="T48" s="8"/>
     </row>
     <row r="49" spans="1:20" ht="28">
-      <c r="A49" s="80"/>
+      <c r="A49" s="82"/>
       <c r="B49" s="50"/>
       <c r="C49" s="49" t="s">
         <v>234</v>
@@ -8098,7 +8103,7 @@
       <c r="T49" s="8"/>
     </row>
     <row r="50" spans="1:20" ht="42">
-      <c r="A50" s="85" t="s">
+      <c r="A50" s="83" t="s">
         <v>240</v>
       </c>
       <c r="B50" s="49" t="s">
@@ -8138,7 +8143,7 @@
       <c r="T50" s="8"/>
     </row>
     <row r="51" spans="1:20" ht="14">
-      <c r="A51" s="85"/>
+      <c r="A51" s="83"/>
       <c r="B51" s="49" t="s">
         <v>92</v>
       </c>
@@ -8176,7 +8181,7 @@
       <c r="T51" s="8"/>
     </row>
     <row r="52" spans="1:20" ht="112">
-      <c r="A52" s="85"/>
+      <c r="A52" s="83"/>
       <c r="B52" s="50"/>
       <c r="C52" s="49" t="s">
         <v>251</v>
@@ -8212,7 +8217,7 @@
       <c r="T52" s="8"/>
     </row>
     <row r="53" spans="1:20" ht="28">
-      <c r="A53" s="85"/>
+      <c r="A53" s="83"/>
       <c r="B53" s="6" t="s">
         <v>85</v>
       </c>
@@ -8241,16 +8246,16 @@
       <c r="K53" s="8"/>
       <c r="L53" s="8"/>
       <c r="M53" s="8"/>
-      <c r="N53" s="76"/>
-      <c r="O53" s="77"/>
-      <c r="P53" s="77"/>
+      <c r="N53" s="77"/>
+      <c r="O53" s="78"/>
+      <c r="P53" s="78"/>
       <c r="Q53" s="8"/>
       <c r="R53" s="8"/>
-      <c r="S53" s="76"/>
-      <c r="T53" s="77"/>
+      <c r="S53" s="77"/>
+      <c r="T53" s="78"/>
     </row>
     <row r="54" spans="1:20" ht="14">
-      <c r="A54" s="85"/>
+      <c r="A54" s="83"/>
       <c r="B54" s="6" t="s">
         <v>92</v>
       </c>
@@ -8260,7 +8265,7 @@
       <c r="D54" s="6" t="s">
         <v>687</v>
       </c>
-      <c r="E54" s="86" t="s">
+      <c r="E54" s="76" t="s">
         <v>1649</v>
       </c>
       <c r="F54" s="9" t="s">
@@ -8278,17 +8283,17 @@
       <c r="J54" s="8"/>
       <c r="K54" s="8"/>
       <c r="L54" s="8"/>
-      <c r="M54" s="76"/>
-      <c r="N54" s="77"/>
+      <c r="M54" s="77"/>
+      <c r="N54" s="78"/>
       <c r="O54" s="8"/>
       <c r="P54" s="8"/>
       <c r="Q54" s="8"/>
-      <c r="R54" s="76"/>
-      <c r="S54" s="77"/>
+      <c r="R54" s="77"/>
+      <c r="S54" s="78"/>
       <c r="T54" s="8"/>
     </row>
     <row r="55" spans="1:20" ht="112">
-      <c r="A55" s="85"/>
+      <c r="A55" s="83"/>
       <c r="B55" s="7"/>
       <c r="C55" s="6" t="s">
         <v>692</v>
@@ -8296,7 +8301,7 @@
       <c r="D55" s="16" t="s">
         <v>693</v>
       </c>
-      <c r="E55" s="86" t="s">
+      <c r="E55" s="76" t="s">
         <v>1650</v>
       </c>
       <c r="F55" s="9" t="s">
@@ -8314,17 +8319,17 @@
       <c r="J55" s="8"/>
       <c r="K55" s="8"/>
       <c r="L55" s="8"/>
-      <c r="M55" s="76"/>
-      <c r="N55" s="77"/>
-      <c r="O55" s="77"/>
+      <c r="M55" s="77"/>
+      <c r="N55" s="78"/>
+      <c r="O55" s="78"/>
       <c r="P55" s="8"/>
       <c r="Q55" s="8"/>
-      <c r="R55" s="76"/>
-      <c r="S55" s="77"/>
-      <c r="T55" s="77"/>
+      <c r="R55" s="77"/>
+      <c r="S55" s="78"/>
+      <c r="T55" s="78"/>
     </row>
     <row r="56" spans="1:20" ht="28">
-      <c r="A56" s="85"/>
+      <c r="A56" s="83"/>
       <c r="B56" s="6" t="s">
         <v>85</v>
       </c>
@@ -8351,7 +8356,7 @@
       </c>
     </row>
     <row r="57" spans="1:20" ht="14">
-      <c r="A57" s="85"/>
+      <c r="A57" s="83"/>
       <c r="B57" s="6" t="s">
         <v>92</v>
       </c>
@@ -8361,7 +8366,7 @@
       <c r="D57" s="6" t="s">
         <v>1039</v>
       </c>
-      <c r="E57" s="86" t="s">
+      <c r="E57" s="76" t="s">
         <v>1651</v>
       </c>
       <c r="F57" s="9" t="s">
@@ -8378,7 +8383,7 @@
       </c>
     </row>
     <row r="58" spans="1:20" ht="112">
-      <c r="A58" s="85"/>
+      <c r="A58" s="83"/>
       <c r="B58" s="7"/>
       <c r="C58" s="6" t="s">
         <v>1044</v>
@@ -8386,7 +8391,7 @@
       <c r="D58" s="6" t="s">
         <v>1045</v>
       </c>
-      <c r="E58" s="86" t="s">
+      <c r="E58" s="76" t="s">
         <v>1652</v>
       </c>
       <c r="F58" s="9" t="s">
@@ -8403,7 +8408,7 @@
       </c>
     </row>
     <row r="59" spans="1:20" ht="42">
-      <c r="A59" s="85"/>
+      <c r="A59" s="83"/>
       <c r="B59" s="6" t="s">
         <v>85</v>
       </c>
@@ -8432,16 +8437,16 @@
       <c r="K59" s="8"/>
       <c r="L59" s="8"/>
       <c r="M59" s="8"/>
-      <c r="N59" s="76"/>
-      <c r="O59" s="77"/>
-      <c r="P59" s="77"/>
+      <c r="N59" s="77"/>
+      <c r="O59" s="78"/>
+      <c r="P59" s="78"/>
       <c r="Q59" s="8"/>
       <c r="R59" s="8"/>
-      <c r="S59" s="76"/>
-      <c r="T59" s="77"/>
+      <c r="S59" s="77"/>
+      <c r="T59" s="78"/>
     </row>
     <row r="60" spans="1:20" ht="28">
-      <c r="A60" s="85"/>
+      <c r="A60" s="83"/>
       <c r="B60" s="6" t="s">
         <v>92</v>
       </c>
@@ -8451,7 +8456,7 @@
       <c r="D60" s="6" t="s">
         <v>1394</v>
       </c>
-      <c r="E60" s="86" t="s">
+      <c r="E60" s="76" t="s">
         <v>1653</v>
       </c>
       <c r="F60" s="9" t="s">
@@ -8469,17 +8474,17 @@
       <c r="J60" s="8"/>
       <c r="K60" s="8"/>
       <c r="L60" s="8"/>
-      <c r="M60" s="76"/>
-      <c r="N60" s="77"/>
+      <c r="M60" s="77"/>
+      <c r="N60" s="78"/>
       <c r="O60" s="8"/>
       <c r="P60" s="8"/>
       <c r="Q60" s="8"/>
-      <c r="R60" s="76"/>
-      <c r="S60" s="77"/>
+      <c r="R60" s="77"/>
+      <c r="S60" s="78"/>
       <c r="T60" s="8"/>
     </row>
     <row r="61" spans="1:20" ht="98">
-      <c r="A61" s="85"/>
+      <c r="A61" s="83"/>
       <c r="B61" s="7"/>
       <c r="C61" s="6" t="s">
         <v>1398</v>
@@ -8487,7 +8492,7 @@
       <c r="D61" s="6" t="s">
         <v>1399</v>
       </c>
-      <c r="E61" s="86" t="s">
+      <c r="E61" s="76" t="s">
         <v>1654</v>
       </c>
       <c r="F61" s="9" t="s">
@@ -8505,14 +8510,14 @@
       <c r="J61" s="8"/>
       <c r="K61" s="8"/>
       <c r="L61" s="8"/>
-      <c r="M61" s="76"/>
-      <c r="N61" s="77"/>
-      <c r="O61" s="77"/>
+      <c r="M61" s="77"/>
+      <c r="N61" s="78"/>
+      <c r="O61" s="78"/>
       <c r="P61" s="8"/>
       <c r="Q61" s="8"/>
-      <c r="R61" s="76"/>
-      <c r="S61" s="77"/>
-      <c r="T61" s="77"/>
+      <c r="R61" s="77"/>
+      <c r="S61" s="78"/>
+      <c r="T61" s="78"/>
     </row>
     <row r="62" spans="1:20" ht="14">
       <c r="A62" s="81" t="s">
@@ -8527,7 +8532,7 @@
       <c r="D62" s="21" t="s">
         <v>699</v>
       </c>
-      <c r="E62" s="86" t="s">
+      <c r="E62" s="76" t="s">
         <v>1655</v>
       </c>
       <c r="F62" s="9" t="s">
@@ -8546,16 +8551,16 @@
       <c r="K62" s="8"/>
       <c r="L62" s="8"/>
       <c r="M62" s="4"/>
-      <c r="N62" s="78"/>
-      <c r="O62" s="77"/>
+      <c r="N62" s="79"/>
+      <c r="O62" s="78"/>
       <c r="P62" s="8"/>
       <c r="Q62" s="4"/>
       <c r="R62" s="4"/>
-      <c r="S62" s="78"/>
-      <c r="T62" s="77"/>
+      <c r="S62" s="79"/>
+      <c r="T62" s="78"/>
     </row>
     <row r="63" spans="1:20" ht="14">
-      <c r="A63" s="80"/>
+      <c r="A63" s="82"/>
       <c r="B63" s="50"/>
       <c r="C63" s="49" t="s">
         <v>260</v>
@@ -8591,7 +8596,7 @@
       <c r="T63" s="8"/>
     </row>
     <row r="64" spans="1:20" ht="154">
-      <c r="A64" s="80"/>
+      <c r="A64" s="82"/>
       <c r="B64" s="49" t="s">
         <v>92</v>
       </c>
@@ -8629,7 +8634,7 @@
       <c r="T64" s="8"/>
     </row>
     <row r="65" spans="1:20" ht="14">
-      <c r="A65" s="80"/>
+      <c r="A65" s="82"/>
       <c r="B65" s="50"/>
       <c r="C65" s="49" t="s">
         <v>268</v>
@@ -8665,7 +8670,7 @@
       <c r="T65" s="8"/>
     </row>
     <row r="66" spans="1:20" ht="140">
-      <c r="A66" s="80"/>
+      <c r="A66" s="82"/>
       <c r="B66" s="50"/>
       <c r="C66" s="49" t="s">
         <v>274</v>
@@ -8701,7 +8706,7 @@
       <c r="T66" s="8"/>
     </row>
     <row r="67" spans="1:20" ht="14">
-      <c r="A67" s="80"/>
+      <c r="A67" s="82"/>
       <c r="B67" s="50"/>
       <c r="C67" s="49" t="s">
         <v>276</v>
@@ -8737,7 +8742,7 @@
       <c r="T67" s="8"/>
     </row>
     <row r="68" spans="1:20" ht="126">
-      <c r="A68" s="80"/>
+      <c r="A68" s="82"/>
       <c r="B68" s="49" t="s">
         <v>85</v>
       </c>
@@ -8775,7 +8780,7 @@
       <c r="T68" s="8"/>
     </row>
     <row r="69" spans="1:20" ht="14">
-      <c r="A69" s="80"/>
+      <c r="A69" s="82"/>
       <c r="B69" s="50"/>
       <c r="C69" s="49" t="s">
         <v>284</v>
@@ -8809,7 +8814,7 @@
       <c r="T69" s="8"/>
     </row>
     <row r="70" spans="1:20" ht="140">
-      <c r="A70" s="80"/>
+      <c r="A70" s="82"/>
       <c r="B70" s="50"/>
       <c r="C70" s="49" t="s">
         <v>285</v>
@@ -8910,13 +8915,13 @@
       <c r="K72" s="8"/>
       <c r="L72" s="8"/>
       <c r="M72" s="4"/>
-      <c r="N72" s="78"/>
-      <c r="O72" s="77"/>
+      <c r="N72" s="79"/>
+      <c r="O72" s="78"/>
       <c r="P72" s="8"/>
       <c r="Q72" s="4"/>
       <c r="R72" s="4"/>
-      <c r="S72" s="78"/>
-      <c r="T72" s="77"/>
+      <c r="S72" s="79"/>
+      <c r="T72" s="78"/>
     </row>
     <row r="73" spans="1:20" ht="84">
       <c r="A73" s="50"/>
@@ -8946,13 +8951,13 @@
       <c r="K73" s="8"/>
       <c r="L73" s="8"/>
       <c r="M73" s="8"/>
-      <c r="N73" s="76"/>
-      <c r="O73" s="77"/>
-      <c r="P73" s="77"/>
+      <c r="N73" s="77"/>
+      <c r="O73" s="78"/>
+      <c r="P73" s="78"/>
       <c r="Q73" s="8"/>
       <c r="R73" s="8"/>
-      <c r="S73" s="76"/>
-      <c r="T73" s="77"/>
+      <c r="S73" s="77"/>
+      <c r="T73" s="78"/>
     </row>
     <row r="74" spans="1:20" ht="28">
       <c r="A74" s="50"/>
@@ -8982,13 +8987,13 @@
       <c r="K74" s="7"/>
       <c r="L74" s="7"/>
       <c r="M74" s="8"/>
-      <c r="N74" s="76"/>
-      <c r="O74" s="77"/>
-      <c r="P74" s="77"/>
+      <c r="N74" s="77"/>
+      <c r="O74" s="78"/>
+      <c r="P74" s="78"/>
       <c r="Q74" s="8"/>
       <c r="R74" s="8"/>
-      <c r="S74" s="76"/>
-      <c r="T74" s="77"/>
+      <c r="S74" s="77"/>
+      <c r="T74" s="78"/>
     </row>
     <row r="75" spans="1:20" ht="70">
       <c r="A75" s="50"/>
@@ -9018,13 +9023,13 @@
       <c r="K75" s="8"/>
       <c r="L75" s="8"/>
       <c r="M75" s="8"/>
-      <c r="N75" s="76"/>
-      <c r="O75" s="77"/>
-      <c r="P75" s="77"/>
+      <c r="N75" s="77"/>
+      <c r="O75" s="78"/>
+      <c r="P75" s="78"/>
       <c r="Q75" s="8"/>
       <c r="R75" s="8"/>
-      <c r="S75" s="76"/>
-      <c r="T75" s="77"/>
+      <c r="S75" s="77"/>
+      <c r="T75" s="78"/>
     </row>
     <row r="76" spans="1:20" ht="28">
       <c r="A76" s="50"/>
@@ -9054,13 +9059,13 @@
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
       <c r="M76" s="8"/>
-      <c r="N76" s="76"/>
-      <c r="O76" s="77"/>
-      <c r="P76" s="77"/>
+      <c r="N76" s="77"/>
+      <c r="O76" s="78"/>
+      <c r="P76" s="78"/>
       <c r="Q76" s="8"/>
       <c r="R76" s="8"/>
-      <c r="S76" s="76"/>
-      <c r="T76" s="77"/>
+      <c r="S76" s="77"/>
+      <c r="T76" s="78"/>
     </row>
     <row r="77" spans="1:20" ht="56">
       <c r="A77" s="50"/>
@@ -9090,13 +9095,13 @@
       <c r="K77" s="8"/>
       <c r="L77" s="8"/>
       <c r="M77" s="8"/>
-      <c r="N77" s="76"/>
-      <c r="O77" s="77"/>
-      <c r="P77" s="77"/>
+      <c r="N77" s="77"/>
+      <c r="O77" s="78"/>
+      <c r="P77" s="78"/>
       <c r="Q77" s="8"/>
       <c r="R77" s="8"/>
-      <c r="S77" s="76"/>
-      <c r="T77" s="77"/>
+      <c r="S77" s="77"/>
+      <c r="T77" s="78"/>
     </row>
     <row r="78" spans="1:20" ht="14">
       <c r="A78" s="50"/>
@@ -9128,13 +9133,13 @@
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
       <c r="M78" s="8"/>
-      <c r="N78" s="76"/>
-      <c r="O78" s="77"/>
-      <c r="P78" s="77"/>
+      <c r="N78" s="77"/>
+      <c r="O78" s="78"/>
+      <c r="P78" s="78"/>
       <c r="Q78" s="8"/>
       <c r="R78" s="8"/>
-      <c r="S78" s="76"/>
-      <c r="T78" s="77"/>
+      <c r="S78" s="77"/>
+      <c r="T78" s="78"/>
     </row>
     <row r="79" spans="1:20" ht="98">
       <c r="A79" s="50"/>
@@ -9166,13 +9171,13 @@
       <c r="K79" s="8"/>
       <c r="L79" s="8"/>
       <c r="M79" s="8"/>
-      <c r="N79" s="76"/>
-      <c r="O79" s="77"/>
-      <c r="P79" s="77"/>
+      <c r="N79" s="77"/>
+      <c r="O79" s="78"/>
+      <c r="P79" s="78"/>
       <c r="Q79" s="8"/>
       <c r="R79" s="8"/>
-      <c r="S79" s="76"/>
-      <c r="T79" s="77"/>
+      <c r="S79" s="77"/>
+      <c r="T79" s="78"/>
     </row>
     <row r="80" spans="1:20" ht="28">
       <c r="A80" s="50"/>
@@ -9202,13 +9207,13 @@
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
       <c r="M80" s="8"/>
-      <c r="N80" s="76"/>
-      <c r="O80" s="77"/>
-      <c r="P80" s="77"/>
+      <c r="N80" s="77"/>
+      <c r="O80" s="78"/>
+      <c r="P80" s="78"/>
       <c r="Q80" s="8"/>
       <c r="R80" s="8"/>
-      <c r="S80" s="76"/>
-      <c r="T80" s="77"/>
+      <c r="S80" s="77"/>
+      <c r="T80" s="78"/>
     </row>
     <row r="81" spans="1:20" ht="84">
       <c r="A81" s="50"/>
@@ -9240,13 +9245,13 @@
       <c r="K81" s="8"/>
       <c r="L81" s="8"/>
       <c r="M81" s="8"/>
-      <c r="N81" s="76"/>
-      <c r="O81" s="77"/>
-      <c r="P81" s="77"/>
+      <c r="N81" s="77"/>
+      <c r="O81" s="78"/>
+      <c r="P81" s="78"/>
       <c r="Q81" s="8"/>
       <c r="R81" s="8"/>
-      <c r="S81" s="76"/>
-      <c r="T81" s="77"/>
+      <c r="S81" s="77"/>
+      <c r="T81" s="78"/>
     </row>
     <row r="82" spans="1:20" ht="28">
       <c r="A82" s="50"/>
@@ -9276,13 +9281,13 @@
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
       <c r="M82" s="8"/>
-      <c r="N82" s="76"/>
-      <c r="O82" s="77"/>
-      <c r="P82" s="77"/>
+      <c r="N82" s="77"/>
+      <c r="O82" s="78"/>
+      <c r="P82" s="78"/>
       <c r="Q82" s="8"/>
       <c r="R82" s="8"/>
-      <c r="S82" s="76"/>
-      <c r="T82" s="77"/>
+      <c r="S82" s="77"/>
+      <c r="T82" s="78"/>
     </row>
     <row r="83" spans="1:20" ht="56">
       <c r="A83" s="50"/>
@@ -9314,13 +9319,13 @@
       <c r="K83" s="8"/>
       <c r="L83" s="8"/>
       <c r="M83" s="8"/>
-      <c r="N83" s="76"/>
-      <c r="O83" s="77"/>
-      <c r="P83" s="77"/>
+      <c r="N83" s="77"/>
+      <c r="O83" s="78"/>
+      <c r="P83" s="78"/>
       <c r="Q83" s="8"/>
       <c r="R83" s="8"/>
-      <c r="S83" s="76"/>
-      <c r="T83" s="77"/>
+      <c r="S83" s="77"/>
+      <c r="T83" s="78"/>
     </row>
     <row r="84" spans="1:20" ht="28">
       <c r="A84" s="50"/>
@@ -9350,16 +9355,16 @@
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
       <c r="M84" s="8"/>
-      <c r="N84" s="76"/>
-      <c r="O84" s="77"/>
-      <c r="P84" s="77"/>
+      <c r="N84" s="77"/>
+      <c r="O84" s="78"/>
+      <c r="P84" s="78"/>
       <c r="Q84" s="8"/>
       <c r="R84" s="8"/>
-      <c r="S84" s="76"/>
-      <c r="T84" s="77"/>
+      <c r="S84" s="77"/>
+      <c r="T84" s="78"/>
     </row>
     <row r="85" spans="1:20" ht="70">
-      <c r="A85" s="87" t="s">
+      <c r="A85" s="84" t="s">
         <v>371</v>
       </c>
       <c r="B85" s="50"/>
@@ -9388,16 +9393,16 @@
       <c r="K85" s="8"/>
       <c r="L85" s="8"/>
       <c r="M85" s="8"/>
-      <c r="N85" s="76"/>
-      <c r="O85" s="77"/>
-      <c r="P85" s="77"/>
+      <c r="N85" s="77"/>
+      <c r="O85" s="78"/>
+      <c r="P85" s="78"/>
       <c r="Q85" s="8"/>
       <c r="R85" s="8"/>
-      <c r="S85" s="76"/>
-      <c r="T85" s="77"/>
+      <c r="S85" s="77"/>
+      <c r="T85" s="78"/>
     </row>
     <row r="86" spans="1:20" ht="28">
-      <c r="A86" s="87"/>
+      <c r="A86" s="84"/>
       <c r="B86" s="50"/>
       <c r="C86" s="49" t="s">
         <v>378</v>
@@ -9423,17 +9428,17 @@
       <c r="J86" s="8"/>
       <c r="K86" s="8"/>
       <c r="L86" s="8"/>
-      <c r="M86" s="76"/>
-      <c r="N86" s="77"/>
-      <c r="O86" s="77"/>
+      <c r="M86" s="77"/>
+      <c r="N86" s="78"/>
+      <c r="O86" s="78"/>
       <c r="P86" s="8"/>
       <c r="Q86" s="8"/>
-      <c r="R86" s="76"/>
-      <c r="S86" s="77"/>
-      <c r="T86" s="77"/>
+      <c r="R86" s="77"/>
+      <c r="S86" s="78"/>
+      <c r="T86" s="78"/>
     </row>
     <row r="87" spans="1:20" ht="56">
-      <c r="A87" s="87"/>
+      <c r="A87" s="84"/>
       <c r="B87" s="50"/>
       <c r="C87" s="49" t="s">
         <v>384</v>
@@ -9459,17 +9464,17 @@
       <c r="J87" s="8"/>
       <c r="K87" s="8"/>
       <c r="L87" s="8"/>
-      <c r="M87" s="76"/>
-      <c r="N87" s="77"/>
-      <c r="O87" s="77"/>
+      <c r="M87" s="77"/>
+      <c r="N87" s="78"/>
+      <c r="O87" s="78"/>
       <c r="P87" s="8"/>
       <c r="Q87" s="8"/>
-      <c r="R87" s="76"/>
-      <c r="S87" s="77"/>
-      <c r="T87" s="77"/>
+      <c r="R87" s="77"/>
+      <c r="S87" s="78"/>
+      <c r="T87" s="78"/>
     </row>
     <row r="88" spans="1:20" ht="28">
-      <c r="A88" s="87"/>
+      <c r="A88" s="84"/>
       <c r="B88" s="50"/>
       <c r="C88" s="49" t="s">
         <v>390</v>
@@ -9495,17 +9500,17 @@
       <c r="J88" s="8"/>
       <c r="K88" s="8"/>
       <c r="L88" s="8"/>
-      <c r="M88" s="76"/>
-      <c r="N88" s="77"/>
-      <c r="O88" s="77"/>
+      <c r="M88" s="77"/>
+      <c r="N88" s="78"/>
+      <c r="O88" s="78"/>
       <c r="P88" s="8"/>
       <c r="Q88" s="8"/>
-      <c r="R88" s="76"/>
-      <c r="S88" s="77"/>
-      <c r="T88" s="77"/>
+      <c r="R88" s="77"/>
+      <c r="S88" s="78"/>
+      <c r="T88" s="78"/>
     </row>
     <row r="89" spans="1:20" ht="70">
-      <c r="A89" s="87"/>
+      <c r="A89" s="84"/>
       <c r="B89" s="50"/>
       <c r="C89" s="49" t="s">
         <v>396</v>
@@ -9531,17 +9536,17 @@
       <c r="J89" s="8"/>
       <c r="K89" s="8"/>
       <c r="L89" s="8"/>
-      <c r="M89" s="76"/>
-      <c r="N89" s="77"/>
-      <c r="O89" s="77"/>
+      <c r="M89" s="77"/>
+      <c r="N89" s="78"/>
+      <c r="O89" s="78"/>
       <c r="P89" s="8"/>
       <c r="Q89" s="8"/>
-      <c r="R89" s="76"/>
-      <c r="S89" s="77"/>
-      <c r="T89" s="77"/>
+      <c r="R89" s="77"/>
+      <c r="S89" s="78"/>
+      <c r="T89" s="78"/>
     </row>
     <row r="90" spans="1:20" ht="42">
-      <c r="A90" s="87"/>
+      <c r="A90" s="84"/>
       <c r="B90" s="50"/>
       <c r="C90" s="49" t="s">
         <v>402</v>
@@ -9567,17 +9572,17 @@
       <c r="J90" s="8"/>
       <c r="K90" s="8"/>
       <c r="L90" s="8"/>
-      <c r="M90" s="76"/>
-      <c r="N90" s="77"/>
-      <c r="O90" s="77"/>
+      <c r="M90" s="77"/>
+      <c r="N90" s="78"/>
+      <c r="O90" s="78"/>
       <c r="P90" s="8"/>
       <c r="Q90" s="8"/>
-      <c r="R90" s="76"/>
-      <c r="S90" s="77"/>
-      <c r="T90" s="77"/>
+      <c r="R90" s="77"/>
+      <c r="S90" s="78"/>
+      <c r="T90" s="78"/>
     </row>
     <row r="91" spans="1:20" ht="56">
-      <c r="A91" s="87"/>
+      <c r="A91" s="84"/>
       <c r="B91" s="50"/>
       <c r="C91" s="49" t="s">
         <v>408</v>
@@ -9603,14 +9608,14 @@
       <c r="J91" s="8"/>
       <c r="K91" s="8"/>
       <c r="L91" s="8"/>
-      <c r="M91" s="76"/>
-      <c r="N91" s="77"/>
-      <c r="O91" s="77"/>
+      <c r="M91" s="77"/>
+      <c r="N91" s="78"/>
+      <c r="O91" s="78"/>
       <c r="P91" s="8"/>
       <c r="Q91" s="8"/>
-      <c r="R91" s="76"/>
-      <c r="S91" s="77"/>
-      <c r="T91" s="77"/>
+      <c r="R91" s="77"/>
+      <c r="S91" s="78"/>
+      <c r="T91" s="78"/>
     </row>
     <row r="92" spans="1:20" ht="14">
       <c r="A92" s="62" t="s">
@@ -9895,117 +9900,21 @@
     </row>
   </sheetData>
   <mergeCells count="150">
-    <mergeCell ref="S74:T74"/>
-    <mergeCell ref="S78:T78"/>
-    <mergeCell ref="N74:P74"/>
-    <mergeCell ref="N75:P75"/>
-    <mergeCell ref="N76:P76"/>
-    <mergeCell ref="N77:P77"/>
-    <mergeCell ref="S77:T77"/>
-    <mergeCell ref="N78:P78"/>
-    <mergeCell ref="M60:N60"/>
-    <mergeCell ref="R60:S60"/>
-    <mergeCell ref="M61:O61"/>
-    <mergeCell ref="N62:O62"/>
-    <mergeCell ref="R61:T61"/>
-    <mergeCell ref="S62:T62"/>
-    <mergeCell ref="N72:O72"/>
-    <mergeCell ref="S72:T72"/>
-    <mergeCell ref="N73:P73"/>
-    <mergeCell ref="S73:T73"/>
-    <mergeCell ref="R43:T43"/>
-    <mergeCell ref="R44:T44"/>
-    <mergeCell ref="M45:O45"/>
-    <mergeCell ref="R45:T45"/>
-    <mergeCell ref="M46:O46"/>
-    <mergeCell ref="R46:T46"/>
-    <mergeCell ref="R47:S47"/>
-    <mergeCell ref="M47:O47"/>
-    <mergeCell ref="N59:P59"/>
-    <mergeCell ref="S59:T59"/>
-    <mergeCell ref="N53:P53"/>
-    <mergeCell ref="S53:T53"/>
-    <mergeCell ref="M54:N54"/>
-    <mergeCell ref="R54:S54"/>
-    <mergeCell ref="M55:O55"/>
-    <mergeCell ref="R55:T55"/>
-    <mergeCell ref="R34:T34"/>
-    <mergeCell ref="R35:T35"/>
-    <mergeCell ref="R39:T39"/>
-    <mergeCell ref="M40:O40"/>
-    <mergeCell ref="R40:T40"/>
-    <mergeCell ref="M41:O41"/>
-    <mergeCell ref="R41:T41"/>
-    <mergeCell ref="S42:T42"/>
-    <mergeCell ref="R37:T37"/>
-    <mergeCell ref="R38:T38"/>
-    <mergeCell ref="M34:O34"/>
-    <mergeCell ref="M35:O35"/>
-    <mergeCell ref="M36:O36"/>
-    <mergeCell ref="R36:T36"/>
-    <mergeCell ref="M37:O37"/>
-    <mergeCell ref="R91:T91"/>
-    <mergeCell ref="S75:T75"/>
-    <mergeCell ref="S76:T76"/>
-    <mergeCell ref="N85:P85"/>
-    <mergeCell ref="S85:T85"/>
-    <mergeCell ref="M86:O86"/>
-    <mergeCell ref="R86:T86"/>
-    <mergeCell ref="R87:T87"/>
-    <mergeCell ref="R88:T88"/>
-    <mergeCell ref="R89:T89"/>
-    <mergeCell ref="S79:T79"/>
-    <mergeCell ref="N79:P79"/>
-    <mergeCell ref="N83:P83"/>
-    <mergeCell ref="N84:P84"/>
-    <mergeCell ref="N80:P80"/>
-    <mergeCell ref="S80:T80"/>
-    <mergeCell ref="N81:P81"/>
-    <mergeCell ref="S81:T81"/>
-    <mergeCell ref="N82:P82"/>
-    <mergeCell ref="S82:T82"/>
-    <mergeCell ref="S83:T83"/>
-    <mergeCell ref="S84:T84"/>
-    <mergeCell ref="M11:O11"/>
-    <mergeCell ref="R11:T11"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="S17:T17"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="S18:T18"/>
-    <mergeCell ref="N19:P19"/>
-    <mergeCell ref="S19:T19"/>
-    <mergeCell ref="M12:O12"/>
-    <mergeCell ref="R12:T12"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="S13:T13"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="S14:T14"/>
-    <mergeCell ref="S15:T15"/>
-    <mergeCell ref="R22:T22"/>
-    <mergeCell ref="S23:T23"/>
-    <mergeCell ref="N15:O15"/>
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="M87:O87"/>
-    <mergeCell ref="M88:O88"/>
-    <mergeCell ref="M89:O89"/>
-    <mergeCell ref="R90:T90"/>
-    <mergeCell ref="A32:A41"/>
-    <mergeCell ref="A42:A49"/>
-    <mergeCell ref="A62:A70"/>
-    <mergeCell ref="M26:O26"/>
-    <mergeCell ref="M27:O27"/>
-    <mergeCell ref="M28:O28"/>
-    <mergeCell ref="M29:O29"/>
-    <mergeCell ref="M30:O30"/>
-    <mergeCell ref="M31:O31"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="M90:O90"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="M43:N43"/>
-    <mergeCell ref="M44:O44"/>
-    <mergeCell ref="M39:O39"/>
-    <mergeCell ref="M91:O91"/>
-    <mergeCell ref="M38:O38"/>
+    <mergeCell ref="R26:T26"/>
+    <mergeCell ref="S16:T16"/>
+    <mergeCell ref="S21:T21"/>
+    <mergeCell ref="M10:O10"/>
+    <mergeCell ref="R10:T10"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="M8:O8"/>
+    <mergeCell ref="R8:T8"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="M24:O24"/>
+    <mergeCell ref="R24:T24"/>
+    <mergeCell ref="M25:O25"/>
+    <mergeCell ref="R25:T25"/>
     <mergeCell ref="A50:A61"/>
     <mergeCell ref="A85:A91"/>
     <mergeCell ref="N2:P2"/>
@@ -10030,21 +9939,117 @@
     <mergeCell ref="M33:O33"/>
     <mergeCell ref="S5:T5"/>
     <mergeCell ref="S6:T6"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="M8:O8"/>
-    <mergeCell ref="R8:T8"/>
-    <mergeCell ref="M9:N9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="M24:O24"/>
-    <mergeCell ref="R24:T24"/>
-    <mergeCell ref="M25:O25"/>
-    <mergeCell ref="R25:T25"/>
-    <mergeCell ref="R26:T26"/>
-    <mergeCell ref="S16:T16"/>
-    <mergeCell ref="S21:T21"/>
-    <mergeCell ref="M10:O10"/>
-    <mergeCell ref="R10:T10"/>
+    <mergeCell ref="R22:T22"/>
+    <mergeCell ref="S23:T23"/>
+    <mergeCell ref="N15:O15"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="M87:O87"/>
+    <mergeCell ref="M88:O88"/>
+    <mergeCell ref="M89:O89"/>
+    <mergeCell ref="R90:T90"/>
+    <mergeCell ref="A32:A41"/>
+    <mergeCell ref="A42:A49"/>
+    <mergeCell ref="A62:A70"/>
+    <mergeCell ref="M26:O26"/>
+    <mergeCell ref="M27:O27"/>
+    <mergeCell ref="M28:O28"/>
+    <mergeCell ref="M29:O29"/>
+    <mergeCell ref="M30:O30"/>
+    <mergeCell ref="M31:O31"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="M90:O90"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="M43:N43"/>
+    <mergeCell ref="M44:O44"/>
+    <mergeCell ref="M39:O39"/>
+    <mergeCell ref="M38:O38"/>
+    <mergeCell ref="M11:O11"/>
+    <mergeCell ref="R11:T11"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="S17:T17"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="S18:T18"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="S19:T19"/>
+    <mergeCell ref="M12:O12"/>
+    <mergeCell ref="R12:T12"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="S13:T13"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="S14:T14"/>
+    <mergeCell ref="S15:T15"/>
+    <mergeCell ref="R91:T91"/>
+    <mergeCell ref="S75:T75"/>
+    <mergeCell ref="S76:T76"/>
+    <mergeCell ref="N85:P85"/>
+    <mergeCell ref="S85:T85"/>
+    <mergeCell ref="M86:O86"/>
+    <mergeCell ref="R86:T86"/>
+    <mergeCell ref="R87:T87"/>
+    <mergeCell ref="R88:T88"/>
+    <mergeCell ref="R89:T89"/>
+    <mergeCell ref="S79:T79"/>
+    <mergeCell ref="N79:P79"/>
+    <mergeCell ref="N83:P83"/>
+    <mergeCell ref="N84:P84"/>
+    <mergeCell ref="N80:P80"/>
+    <mergeCell ref="S80:T80"/>
+    <mergeCell ref="N81:P81"/>
+    <mergeCell ref="S81:T81"/>
+    <mergeCell ref="N82:P82"/>
+    <mergeCell ref="S82:T82"/>
+    <mergeCell ref="S83:T83"/>
+    <mergeCell ref="S84:T84"/>
+    <mergeCell ref="M91:O91"/>
+    <mergeCell ref="R34:T34"/>
+    <mergeCell ref="R35:T35"/>
+    <mergeCell ref="R39:T39"/>
+    <mergeCell ref="M40:O40"/>
+    <mergeCell ref="R40:T40"/>
+    <mergeCell ref="M41:O41"/>
+    <mergeCell ref="R41:T41"/>
+    <mergeCell ref="S42:T42"/>
+    <mergeCell ref="R37:T37"/>
+    <mergeCell ref="R38:T38"/>
+    <mergeCell ref="M34:O34"/>
+    <mergeCell ref="M35:O35"/>
+    <mergeCell ref="M36:O36"/>
+    <mergeCell ref="R36:T36"/>
+    <mergeCell ref="M37:O37"/>
+    <mergeCell ref="R43:T43"/>
+    <mergeCell ref="R44:T44"/>
+    <mergeCell ref="M45:O45"/>
+    <mergeCell ref="R45:T45"/>
+    <mergeCell ref="M46:O46"/>
+    <mergeCell ref="R46:T46"/>
+    <mergeCell ref="R47:S47"/>
+    <mergeCell ref="M47:O47"/>
+    <mergeCell ref="N59:P59"/>
+    <mergeCell ref="S59:T59"/>
+    <mergeCell ref="N53:P53"/>
+    <mergeCell ref="S53:T53"/>
+    <mergeCell ref="M54:N54"/>
+    <mergeCell ref="R54:S54"/>
+    <mergeCell ref="M55:O55"/>
+    <mergeCell ref="R55:T55"/>
+    <mergeCell ref="S74:T74"/>
+    <mergeCell ref="S78:T78"/>
+    <mergeCell ref="N74:P74"/>
+    <mergeCell ref="N75:P75"/>
+    <mergeCell ref="N76:P76"/>
+    <mergeCell ref="N77:P77"/>
+    <mergeCell ref="S77:T77"/>
+    <mergeCell ref="N78:P78"/>
+    <mergeCell ref="M60:N60"/>
+    <mergeCell ref="R60:S60"/>
+    <mergeCell ref="M61:O61"/>
+    <mergeCell ref="N62:O62"/>
+    <mergeCell ref="R61:T61"/>
+    <mergeCell ref="S62:T62"/>
+    <mergeCell ref="N72:O72"/>
+    <mergeCell ref="S72:T72"/>
+    <mergeCell ref="N73:P73"/>
+    <mergeCell ref="S73:T73"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -10187,7 +10192,7 @@
       <c r="I5" s="12"/>
     </row>
     <row r="6" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A6" s="84" t="s">
+      <c r="A6" s="87" t="s">
         <v>30</v>
       </c>
       <c r="B6" s="13" t="s">
@@ -10213,7 +10218,7 @@
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A7" s="77"/>
+      <c r="A7" s="78"/>
       <c r="B7" s="15" t="s">
         <v>35</v>
       </c>
@@ -10227,7 +10232,7 @@
       <c r="I7" s="12"/>
     </row>
     <row r="8" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A8" s="77"/>
+      <c r="A8" s="78"/>
       <c r="B8" s="15" t="s">
         <v>31</v>
       </c>
@@ -10251,7 +10256,7 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A9" s="77"/>
+      <c r="A9" s="78"/>
       <c r="B9" s="15" t="s">
         <v>35</v>
       </c>
@@ -10265,7 +10270,7 @@
       <c r="I9" s="12"/>
     </row>
     <row r="10" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A10" s="77"/>
+      <c r="A10" s="78"/>
       <c r="B10" s="15" t="s">
         <v>31</v>
       </c>
@@ -10289,7 +10294,7 @@
       </c>
     </row>
     <row r="11" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A11" s="77"/>
+      <c r="A11" s="78"/>
       <c r="B11" s="15" t="s">
         <v>40</v>
       </c>
@@ -10313,7 +10318,7 @@
       </c>
     </row>
     <row r="12" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A12" s="77"/>
+      <c r="A12" s="78"/>
       <c r="B12" s="15" t="s">
         <v>45</v>
       </c>
@@ -10515,7 +10520,7 @@
       </c>
     </row>
     <row r="21" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A21" s="83" t="s">
+      <c r="A21" s="86" t="s">
         <v>70</v>
       </c>
       <c r="B21" s="6" t="s">
@@ -10541,7 +10546,7 @@
       </c>
     </row>
     <row r="22" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A22" s="77"/>
+      <c r="A22" s="78"/>
       <c r="B22" s="7"/>
       <c r="C22" s="6" t="s">
         <v>520</v>
@@ -10563,7 +10568,7 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="51">
-      <c r="A23" s="83" t="s">
+      <c r="A23" s="86" t="s">
         <v>84</v>
       </c>
       <c r="B23" s="6" t="s">
@@ -10589,7 +10594,7 @@
       </c>
     </row>
     <row r="24" spans="1:9" ht="17">
-      <c r="A24" s="77"/>
+      <c r="A24" s="78"/>
       <c r="B24" s="6" t="s">
         <v>92</v>
       </c>
@@ -10613,7 +10618,7 @@
       </c>
     </row>
     <row r="25" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A25" s="77"/>
+      <c r="A25" s="78"/>
       <c r="B25" s="7"/>
       <c r="C25" s="6" t="s">
         <v>538</v>
@@ -10635,7 +10640,7 @@
       </c>
     </row>
     <row r="26" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A26" s="77"/>
+      <c r="A26" s="78"/>
       <c r="B26" s="6" t="s">
         <v>92</v>
       </c>
@@ -10659,7 +10664,7 @@
       </c>
     </row>
     <row r="27" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A27" s="77"/>
+      <c r="A27" s="78"/>
       <c r="B27" s="7"/>
       <c r="C27" s="6" t="s">
         <v>550</v>
@@ -10681,7 +10686,7 @@
       </c>
     </row>
     <row r="28" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A28" s="77"/>
+      <c r="A28" s="78"/>
       <c r="B28" s="6" t="s">
         <v>92</v>
       </c>
@@ -10705,7 +10710,7 @@
       </c>
     </row>
     <row r="29" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A29" s="77"/>
+      <c r="A29" s="78"/>
       <c r="B29" s="7"/>
       <c r="C29" s="6" t="s">
         <v>562</v>
@@ -10727,7 +10732,7 @@
       </c>
     </row>
     <row r="30" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A30" s="77"/>
+      <c r="A30" s="78"/>
       <c r="B30" s="6" t="s">
         <v>92</v>
       </c>
@@ -10751,7 +10756,7 @@
       </c>
     </row>
     <row r="31" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A31" s="77"/>
+      <c r="A31" s="78"/>
       <c r="B31" s="7"/>
       <c r="C31" s="6" t="s">
         <v>574</v>
@@ -10773,7 +10778,7 @@
       </c>
     </row>
     <row r="32" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A32" s="83" t="s">
+      <c r="A32" s="86" t="s">
         <v>141</v>
       </c>
       <c r="B32" s="6" t="s">
@@ -10799,7 +10804,7 @@
       </c>
     </row>
     <row r="33" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A33" s="77"/>
+      <c r="A33" s="78"/>
       <c r="B33" s="7"/>
       <c r="C33" s="6" t="s">
         <v>586</v>
@@ -10821,7 +10826,7 @@
       </c>
     </row>
     <row r="34" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A34" s="77"/>
+      <c r="A34" s="78"/>
       <c r="B34" s="6" t="s">
         <v>92</v>
       </c>
@@ -10845,7 +10850,7 @@
       </c>
     </row>
     <row r="35" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A35" s="77"/>
+      <c r="A35" s="78"/>
       <c r="B35" s="7"/>
       <c r="C35" s="6" t="s">
         <v>598</v>
@@ -10867,7 +10872,7 @@
       </c>
     </row>
     <row r="36" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A36" s="77"/>
+      <c r="A36" s="78"/>
       <c r="B36" s="6" t="s">
         <v>92</v>
       </c>
@@ -10891,7 +10896,7 @@
       </c>
     </row>
     <row r="37" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A37" s="77"/>
+      <c r="A37" s="78"/>
       <c r="B37" s="7"/>
       <c r="C37" s="6" t="s">
         <v>610</v>
@@ -10913,7 +10918,7 @@
       </c>
     </row>
     <row r="38" spans="1:9" ht="28">
-      <c r="A38" s="77"/>
+      <c r="A38" s="78"/>
       <c r="B38" s="6" t="s">
         <v>92</v>
       </c>
@@ -10937,7 +10942,7 @@
       </c>
     </row>
     <row r="39" spans="1:9" ht="126">
-      <c r="A39" s="77"/>
+      <c r="A39" s="78"/>
       <c r="B39" s="7"/>
       <c r="C39" s="6" t="s">
         <v>622</v>
@@ -10959,7 +10964,7 @@
       </c>
     </row>
     <row r="40" spans="1:9" ht="28">
-      <c r="A40" s="77"/>
+      <c r="A40" s="78"/>
       <c r="B40" s="6" t="s">
         <v>92</v>
       </c>
@@ -10983,7 +10988,7 @@
       </c>
     </row>
     <row r="41" spans="1:9" ht="140">
-      <c r="A41" s="77"/>
+      <c r="A41" s="78"/>
       <c r="B41" s="7"/>
       <c r="C41" s="6" t="s">
         <v>634</v>
@@ -11005,7 +11010,7 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="28">
-      <c r="A42" s="83" t="s">
+      <c r="A42" s="86" t="s">
         <v>202</v>
       </c>
       <c r="B42" s="6" t="s">
@@ -11031,7 +11036,7 @@
       </c>
     </row>
     <row r="43" spans="1:9" ht="14">
-      <c r="A43" s="77"/>
+      <c r="A43" s="78"/>
       <c r="B43" s="7"/>
       <c r="C43" s="6" t="s">
         <v>646</v>
@@ -11053,7 +11058,7 @@
       </c>
     </row>
     <row r="44" spans="1:9" ht="56">
-      <c r="A44" s="77"/>
+      <c r="A44" s="78"/>
       <c r="B44" s="7"/>
       <c r="C44" s="6" t="s">
         <v>652</v>
@@ -11075,7 +11080,7 @@
       </c>
     </row>
     <row r="45" spans="1:9" ht="28">
-      <c r="A45" s="77"/>
+      <c r="A45" s="78"/>
       <c r="B45" s="7"/>
       <c r="C45" s="6" t="s">
         <v>658</v>
@@ -11097,7 +11102,7 @@
       </c>
     </row>
     <row r="46" spans="1:9" ht="42">
-      <c r="A46" s="77"/>
+      <c r="A46" s="78"/>
       <c r="B46" s="7"/>
       <c r="C46" s="6" t="s">
         <v>664</v>
@@ -11119,7 +11124,7 @@
       </c>
     </row>
     <row r="47" spans="1:9" ht="14">
-      <c r="A47" s="77"/>
+      <c r="A47" s="78"/>
       <c r="B47" s="7"/>
       <c r="C47" s="6" t="s">
         <v>670</v>
@@ -11141,7 +11146,7 @@
       </c>
     </row>
     <row r="48" spans="1:9" ht="42">
-      <c r="A48" s="77"/>
+      <c r="A48" s="78"/>
       <c r="B48" s="7"/>
       <c r="C48" s="6" t="s">
         <v>676</v>
@@ -11163,7 +11168,7 @@
       </c>
     </row>
     <row r="49" spans="1:9" ht="28">
-      <c r="A49" s="85" t="s">
+      <c r="A49" s="83" t="s">
         <v>240</v>
       </c>
       <c r="B49" s="49" t="s">
@@ -11192,7 +11197,7 @@
       </c>
     </row>
     <row r="50" spans="1:9" ht="14">
-      <c r="A50" s="85"/>
+      <c r="A50" s="83"/>
       <c r="B50" s="49" t="s">
         <v>92</v>
       </c>
@@ -11219,7 +11224,7 @@
       </c>
     </row>
     <row r="51" spans="1:9" ht="84">
-      <c r="A51" s="85"/>
+      <c r="A51" s="83"/>
       <c r="B51" s="50"/>
       <c r="C51" s="49" t="s">
         <v>251</v>
@@ -11244,7 +11249,7 @@
       </c>
     </row>
     <row r="52" spans="1:9" ht="28">
-      <c r="A52" s="85"/>
+      <c r="A52" s="83"/>
       <c r="B52" s="6" t="s">
         <v>85</v>
       </c>
@@ -11271,7 +11276,7 @@
       </c>
     </row>
     <row r="53" spans="1:9" ht="14">
-      <c r="A53" s="85"/>
+      <c r="A53" s="83"/>
       <c r="B53" s="6" t="s">
         <v>92</v>
       </c>
@@ -11281,7 +11286,7 @@
       <c r="D53" s="6" t="s">
         <v>687</v>
       </c>
-      <c r="E53" s="86" t="s">
+      <c r="E53" s="76" t="s">
         <v>1649</v>
       </c>
       <c r="F53" s="9" t="s">
@@ -11298,7 +11303,7 @@
       </c>
     </row>
     <row r="54" spans="1:9" ht="70">
-      <c r="A54" s="85"/>
+      <c r="A54" s="83"/>
       <c r="B54" s="7"/>
       <c r="C54" s="6" t="s">
         <v>692</v>
@@ -11306,7 +11311,7 @@
       <c r="D54" s="16" t="s">
         <v>693</v>
       </c>
-      <c r="E54" s="86" t="s">
+      <c r="E54" s="76" t="s">
         <v>1650</v>
       </c>
       <c r="F54" s="9" t="s">
@@ -11323,7 +11328,7 @@
       </c>
     </row>
     <row r="55" spans="1:9" ht="28">
-      <c r="A55" s="85"/>
+      <c r="A55" s="83"/>
       <c r="B55" s="6" t="s">
         <v>85</v>
       </c>
@@ -11350,7 +11355,7 @@
       </c>
     </row>
     <row r="56" spans="1:9" ht="14">
-      <c r="A56" s="85"/>
+      <c r="A56" s="83"/>
       <c r="B56" s="6" t="s">
         <v>92</v>
       </c>
@@ -11360,7 +11365,7 @@
       <c r="D56" s="6" t="s">
         <v>1039</v>
       </c>
-      <c r="E56" s="86" t="s">
+      <c r="E56" s="76" t="s">
         <v>1651</v>
       </c>
       <c r="F56" s="9" t="s">
@@ -11377,7 +11382,7 @@
       </c>
     </row>
     <row r="57" spans="1:9" ht="84">
-      <c r="A57" s="85"/>
+      <c r="A57" s="83"/>
       <c r="B57" s="7"/>
       <c r="C57" s="6" t="s">
         <v>1044</v>
@@ -11385,7 +11390,7 @@
       <c r="D57" s="6" t="s">
         <v>1045</v>
       </c>
-      <c r="E57" s="86" t="s">
+      <c r="E57" s="76" t="s">
         <v>1652</v>
       </c>
       <c r="F57" s="9" t="s">
@@ -11402,7 +11407,7 @@
       </c>
     </row>
     <row r="58" spans="1:9" ht="28">
-      <c r="A58" s="85"/>
+      <c r="A58" s="83"/>
       <c r="B58" s="6" t="s">
         <v>85</v>
       </c>
@@ -11429,7 +11434,7 @@
       </c>
     </row>
     <row r="59" spans="1:9" ht="14">
-      <c r="A59" s="85"/>
+      <c r="A59" s="83"/>
       <c r="B59" s="6" t="s">
         <v>92</v>
       </c>
@@ -11439,7 +11444,7 @@
       <c r="D59" s="6" t="s">
         <v>1394</v>
       </c>
-      <c r="E59" s="86" t="s">
+      <c r="E59" s="76" t="s">
         <v>1653</v>
       </c>
       <c r="F59" s="9" t="s">
@@ -11456,7 +11461,7 @@
       </c>
     </row>
     <row r="60" spans="1:9" ht="70">
-      <c r="A60" s="85"/>
+      <c r="A60" s="83"/>
       <c r="B60" s="7"/>
       <c r="C60" s="6" t="s">
         <v>1398</v>
@@ -11464,7 +11469,7 @@
       <c r="D60" s="6" t="s">
         <v>1399</v>
       </c>
-      <c r="E60" s="86" t="s">
+      <c r="E60" s="76" t="s">
         <v>1654</v>
       </c>
       <c r="F60" s="9" t="s">
@@ -11481,7 +11486,7 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="14">
-      <c r="A61" s="83" t="s">
+      <c r="A61" s="86" t="s">
         <v>257</v>
       </c>
       <c r="B61" s="6" t="s">
@@ -11507,7 +11512,7 @@
       </c>
     </row>
     <row r="62" spans="1:9" ht="14">
-      <c r="A62" s="83"/>
+      <c r="A62" s="86"/>
       <c r="B62" s="7"/>
       <c r="C62" s="6" t="s">
         <v>704</v>
@@ -11529,7 +11534,7 @@
       </c>
     </row>
     <row r="63" spans="1:9" ht="98">
-      <c r="A63" s="83"/>
+      <c r="A63" s="86"/>
       <c r="B63" s="6" t="s">
         <v>92</v>
       </c>
@@ -11553,7 +11558,7 @@
       </c>
     </row>
     <row r="64" spans="1:9" ht="14">
-      <c r="A64" s="83"/>
+      <c r="A64" s="86"/>
       <c r="B64" s="7"/>
       <c r="C64" s="6" t="s">
         <v>712</v>
@@ -11575,7 +11580,7 @@
       </c>
     </row>
     <row r="65" spans="1:9" ht="98">
-      <c r="A65" s="83"/>
+      <c r="A65" s="86"/>
       <c r="B65" s="7"/>
       <c r="C65" s="6" t="s">
         <v>714</v>
@@ -11597,7 +11602,7 @@
       </c>
     </row>
     <row r="66" spans="1:9" ht="14">
-      <c r="A66" s="83"/>
+      <c r="A66" s="86"/>
       <c r="B66" s="7"/>
       <c r="C66" s="6" t="s">
         <v>720</v>
@@ -11619,7 +11624,7 @@
       </c>
     </row>
     <row r="67" spans="1:9" ht="98">
-      <c r="A67" s="83"/>
+      <c r="A67" s="86"/>
       <c r="B67" s="6" t="s">
         <v>85</v>
       </c>
@@ -11643,7 +11648,7 @@
       </c>
     </row>
     <row r="68" spans="1:9" ht="14">
-      <c r="A68" s="83"/>
+      <c r="A68" s="86"/>
       <c r="B68" s="7"/>
       <c r="C68" s="6" t="s">
         <v>728</v>
@@ -11665,7 +11670,7 @@
       </c>
     </row>
     <row r="69" spans="1:9" ht="98">
-      <c r="A69" s="83"/>
+      <c r="A69" s="86"/>
       <c r="B69" s="7"/>
       <c r="C69" s="6" t="s">
         <v>730</v>
@@ -11983,7 +11988,7 @@
       </c>
     </row>
     <row r="83" spans="1:9" ht="28">
-      <c r="A83" s="84" t="s">
+      <c r="A83" s="87" t="s">
         <v>371</v>
       </c>
       <c r="B83" s="7"/>
@@ -12007,7 +12012,7 @@
       </c>
     </row>
     <row r="84" spans="1:9" ht="56">
-      <c r="A84" s="77"/>
+      <c r="A84" s="78"/>
       <c r="B84" s="7"/>
       <c r="C84" s="6" t="s">
         <v>372</v>
@@ -12029,7 +12034,7 @@
       </c>
     </row>
     <row r="85" spans="1:9" ht="28">
-      <c r="A85" s="77"/>
+      <c r="A85" s="78"/>
       <c r="B85" s="7"/>
       <c r="C85" s="6" t="s">
         <v>378</v>
@@ -12051,7 +12056,7 @@
       </c>
     </row>
     <row r="86" spans="1:9" ht="56">
-      <c r="A86" s="77"/>
+      <c r="A86" s="78"/>
       <c r="B86" s="7"/>
       <c r="C86" s="6" t="s">
         <v>384</v>
@@ -12073,7 +12078,7 @@
       </c>
     </row>
     <row r="87" spans="1:9" ht="42">
-      <c r="A87" s="77"/>
+      <c r="A87" s="78"/>
       <c r="B87" s="7"/>
       <c r="C87" s="6" t="s">
         <v>390</v>
@@ -12095,7 +12100,7 @@
       </c>
     </row>
     <row r="88" spans="1:9" ht="56">
-      <c r="A88" s="77"/>
+      <c r="A88" s="78"/>
       <c r="B88" s="7"/>
       <c r="C88" s="6" t="s">
         <v>396</v>
@@ -12117,7 +12122,7 @@
       </c>
     </row>
     <row r="89" spans="1:9" ht="28">
-      <c r="A89" s="77"/>
+      <c r="A89" s="78"/>
       <c r="B89" s="7"/>
       <c r="C89" s="6" t="s">
         <v>402</v>
@@ -12139,7 +12144,7 @@
       </c>
     </row>
     <row r="90" spans="1:9" ht="56">
-      <c r="A90" s="77"/>
+      <c r="A90" s="78"/>
       <c r="B90" s="7"/>
       <c r="C90" s="6" t="s">
         <v>408</v>
@@ -17934,7 +17939,7 @@
       <c r="I5" s="12"/>
     </row>
     <row r="6" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A6" s="84" t="s">
+      <c r="A6" s="87" t="s">
         <v>30</v>
       </c>
       <c r="B6" s="13" t="s">
@@ -17960,7 +17965,7 @@
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A7" s="77"/>
+      <c r="A7" s="78"/>
       <c r="B7" s="15" t="s">
         <v>35</v>
       </c>
@@ -17974,7 +17979,7 @@
       <c r="I7" s="12"/>
     </row>
     <row r="8" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A8" s="77"/>
+      <c r="A8" s="78"/>
       <c r="B8" s="15" t="s">
         <v>31</v>
       </c>
@@ -17998,7 +18003,7 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A9" s="77"/>
+      <c r="A9" s="78"/>
       <c r="B9" s="15" t="s">
         <v>35</v>
       </c>
@@ -18012,7 +18017,7 @@
       <c r="I9" s="12"/>
     </row>
     <row r="10" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A10" s="77"/>
+      <c r="A10" s="78"/>
       <c r="B10" s="15" t="s">
         <v>31</v>
       </c>
@@ -18036,7 +18041,7 @@
       </c>
     </row>
     <row r="11" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A11" s="77"/>
+      <c r="A11" s="78"/>
       <c r="B11" s="15" t="s">
         <v>40</v>
       </c>
@@ -18060,7 +18065,7 @@
       </c>
     </row>
     <row r="12" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A12" s="77"/>
+      <c r="A12" s="78"/>
       <c r="B12" s="15" t="s">
         <v>45</v>
       </c>
@@ -18244,7 +18249,7 @@
       <c r="I20" s="12"/>
     </row>
     <row r="21" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A21" s="83" t="s">
+      <c r="A21" s="86" t="s">
         <v>70</v>
       </c>
       <c r="B21" s="6" t="s">
@@ -18270,7 +18275,7 @@
       </c>
     </row>
     <row r="22" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A22" s="77"/>
+      <c r="A22" s="78"/>
       <c r="B22" s="7"/>
       <c r="C22" s="6" t="s">
         <v>879</v>
@@ -18292,7 +18297,7 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A23" s="83" t="s">
+      <c r="A23" s="86" t="s">
         <v>84</v>
       </c>
       <c r="B23" s="6" t="s">
@@ -18318,7 +18323,7 @@
       </c>
     </row>
     <row r="24" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A24" s="77"/>
+      <c r="A24" s="78"/>
       <c r="B24" s="6" t="s">
         <v>92</v>
       </c>
@@ -18342,7 +18347,7 @@
       </c>
     </row>
     <row r="25" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A25" s="77"/>
+      <c r="A25" s="78"/>
       <c r="B25" s="7"/>
       <c r="C25" s="6" t="s">
         <v>897</v>
@@ -18364,7 +18369,7 @@
       </c>
     </row>
     <row r="26" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A26" s="77"/>
+      <c r="A26" s="78"/>
       <c r="B26" s="6" t="s">
         <v>92</v>
       </c>
@@ -18388,7 +18393,7 @@
       </c>
     </row>
     <row r="27" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A27" s="77"/>
+      <c r="A27" s="78"/>
       <c r="B27" s="7"/>
       <c r="C27" s="6" t="s">
         <v>909</v>
@@ -18410,7 +18415,7 @@
       </c>
     </row>
     <row r="28" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A28" s="77"/>
+      <c r="A28" s="78"/>
       <c r="B28" s="6" t="s">
         <v>92</v>
       </c>
@@ -18434,7 +18439,7 @@
       </c>
     </row>
     <row r="29" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A29" s="77"/>
+      <c r="A29" s="78"/>
       <c r="B29" s="7"/>
       <c r="C29" s="6" t="s">
         <v>921</v>
@@ -18456,7 +18461,7 @@
       </c>
     </row>
     <row r="30" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A30" s="77"/>
+      <c r="A30" s="78"/>
       <c r="B30" s="6" t="s">
         <v>92</v>
       </c>
@@ -18480,7 +18485,7 @@
       </c>
     </row>
     <row r="31" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A31" s="77"/>
+      <c r="A31" s="78"/>
       <c r="B31" s="7"/>
       <c r="C31" s="6" t="s">
         <v>933</v>
@@ -18502,7 +18507,7 @@
       </c>
     </row>
     <row r="32" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A32" s="83" t="s">
+      <c r="A32" s="86" t="s">
         <v>141</v>
       </c>
       <c r="B32" s="6" t="s">
@@ -18528,7 +18533,7 @@
       </c>
     </row>
     <row r="33" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A33" s="77"/>
+      <c r="A33" s="78"/>
       <c r="B33" s="7"/>
       <c r="C33" s="6" t="s">
         <v>945</v>
@@ -18550,7 +18555,7 @@
       </c>
     </row>
     <row r="34" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A34" s="77"/>
+      <c r="A34" s="78"/>
       <c r="B34" s="6" t="s">
         <v>92</v>
       </c>
@@ -18574,7 +18579,7 @@
       </c>
     </row>
     <row r="35" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A35" s="77"/>
+      <c r="A35" s="78"/>
       <c r="B35" s="7"/>
       <c r="C35" s="6" t="s">
         <v>957</v>
@@ -18596,7 +18601,7 @@
       </c>
     </row>
     <row r="36" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A36" s="77"/>
+      <c r="A36" s="78"/>
       <c r="B36" s="6" t="s">
         <v>92</v>
       </c>
@@ -18620,7 +18625,7 @@
       </c>
     </row>
     <row r="37" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A37" s="77"/>
+      <c r="A37" s="78"/>
       <c r="B37" s="7"/>
       <c r="C37" s="6" t="s">
         <v>969</v>
@@ -18642,7 +18647,7 @@
       </c>
     </row>
     <row r="38" spans="1:9" ht="28">
-      <c r="A38" s="77"/>
+      <c r="A38" s="78"/>
       <c r="B38" s="6" t="s">
         <v>92</v>
       </c>
@@ -18666,7 +18671,7 @@
       </c>
     </row>
     <row r="39" spans="1:9" ht="98">
-      <c r="A39" s="77"/>
+      <c r="A39" s="78"/>
       <c r="B39" s="7"/>
       <c r="C39" s="6" t="s">
         <v>981</v>
@@ -18688,7 +18693,7 @@
       </c>
     </row>
     <row r="40" spans="1:9" ht="28">
-      <c r="A40" s="77"/>
+      <c r="A40" s="78"/>
       <c r="B40" s="6" t="s">
         <v>92</v>
       </c>
@@ -18712,7 +18717,7 @@
       </c>
     </row>
     <row r="41" spans="1:9" ht="84">
-      <c r="A41" s="77"/>
+      <c r="A41" s="78"/>
       <c r="B41" s="7"/>
       <c r="C41" s="6" t="s">
         <v>993</v>
@@ -18734,7 +18739,7 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="14">
-      <c r="A42" s="83" t="s">
+      <c r="A42" s="86" t="s">
         <v>202</v>
       </c>
       <c r="B42" s="6" t="s">
@@ -18760,7 +18765,7 @@
       </c>
     </row>
     <row r="43" spans="1:9" ht="14">
-      <c r="A43" s="77"/>
+      <c r="A43" s="78"/>
       <c r="B43" s="7"/>
       <c r="C43" s="6" t="s">
         <v>1005</v>
@@ -18782,7 +18787,7 @@
       </c>
     </row>
     <row r="44" spans="1:9" ht="28">
-      <c r="A44" s="77"/>
+      <c r="A44" s="78"/>
       <c r="B44" s="7"/>
       <c r="C44" s="6" t="s">
         <v>1011</v>
@@ -18804,7 +18809,7 @@
       </c>
     </row>
     <row r="45" spans="1:9" ht="28">
-      <c r="A45" s="77"/>
+      <c r="A45" s="78"/>
       <c r="B45" s="7"/>
       <c r="C45" s="6" t="s">
         <v>1017</v>
@@ -18826,7 +18831,7 @@
       </c>
     </row>
     <row r="46" spans="1:9" ht="42">
-      <c r="A46" s="77"/>
+      <c r="A46" s="78"/>
       <c r="B46" s="7"/>
       <c r="C46" s="6" t="s">
         <v>1021</v>
@@ -18848,7 +18853,7 @@
       </c>
     </row>
     <row r="47" spans="1:9" ht="28">
-      <c r="A47" s="77"/>
+      <c r="A47" s="78"/>
       <c r="B47" s="7"/>
       <c r="C47" s="6" t="s">
         <v>1025</v>
@@ -18870,7 +18875,7 @@
       </c>
     </row>
     <row r="48" spans="1:9" ht="14">
-      <c r="A48" s="77"/>
+      <c r="A48" s="78"/>
       <c r="B48" s="7"/>
       <c r="C48" s="6" t="s">
         <v>1031</v>
@@ -18892,7 +18897,7 @@
       </c>
     </row>
     <row r="49" spans="1:9" ht="28">
-      <c r="A49" s="85" t="s">
+      <c r="A49" s="83" t="s">
         <v>240</v>
       </c>
       <c r="B49" s="49" t="s">
@@ -18921,7 +18926,7 @@
       </c>
     </row>
     <row r="50" spans="1:9" ht="14">
-      <c r="A50" s="85"/>
+      <c r="A50" s="83"/>
       <c r="B50" s="49" t="s">
         <v>92</v>
       </c>
@@ -18948,7 +18953,7 @@
       </c>
     </row>
     <row r="51" spans="1:9" ht="70">
-      <c r="A51" s="85"/>
+      <c r="A51" s="83"/>
       <c r="B51" s="50"/>
       <c r="C51" s="49" t="s">
         <v>251</v>
@@ -18973,7 +18978,7 @@
       </c>
     </row>
     <row r="52" spans="1:9" ht="28">
-      <c r="A52" s="85"/>
+      <c r="A52" s="83"/>
       <c r="B52" s="6" t="s">
         <v>85</v>
       </c>
@@ -19000,7 +19005,7 @@
       </c>
     </row>
     <row r="53" spans="1:9" ht="14">
-      <c r="A53" s="85"/>
+      <c r="A53" s="83"/>
       <c r="B53" s="6" t="s">
         <v>92</v>
       </c>
@@ -19010,7 +19015,7 @@
       <c r="D53" s="6" t="s">
         <v>687</v>
       </c>
-      <c r="E53" s="86" t="s">
+      <c r="E53" s="76" t="s">
         <v>1649</v>
       </c>
       <c r="F53" s="9" t="s">
@@ -19027,7 +19032,7 @@
       </c>
     </row>
     <row r="54" spans="1:9" ht="70">
-      <c r="A54" s="85"/>
+      <c r="A54" s="83"/>
       <c r="B54" s="7"/>
       <c r="C54" s="6" t="s">
         <v>692</v>
@@ -19035,7 +19040,7 @@
       <c r="D54" s="16" t="s">
         <v>693</v>
       </c>
-      <c r="E54" s="86" t="s">
+      <c r="E54" s="76" t="s">
         <v>1650</v>
       </c>
       <c r="F54" s="9" t="s">
@@ -19052,7 +19057,7 @@
       </c>
     </row>
     <row r="55" spans="1:9" ht="28">
-      <c r="A55" s="85"/>
+      <c r="A55" s="83"/>
       <c r="B55" s="6" t="s">
         <v>85</v>
       </c>
@@ -19079,7 +19084,7 @@
       </c>
     </row>
     <row r="56" spans="1:9" ht="14">
-      <c r="A56" s="85"/>
+      <c r="A56" s="83"/>
       <c r="B56" s="6" t="s">
         <v>92</v>
       </c>
@@ -19089,7 +19094,7 @@
       <c r="D56" s="6" t="s">
         <v>1039</v>
       </c>
-      <c r="E56" s="86" t="s">
+      <c r="E56" s="76" t="s">
         <v>1651</v>
       </c>
       <c r="F56" s="9" t="s">
@@ -19106,7 +19111,7 @@
       </c>
     </row>
     <row r="57" spans="1:9" ht="70">
-      <c r="A57" s="85"/>
+      <c r="A57" s="83"/>
       <c r="B57" s="7"/>
       <c r="C57" s="6" t="s">
         <v>1044</v>
@@ -19114,7 +19119,7 @@
       <c r="D57" s="6" t="s">
         <v>1045</v>
       </c>
-      <c r="E57" s="86" t="s">
+      <c r="E57" s="76" t="s">
         <v>1652</v>
       </c>
       <c r="F57" s="9" t="s">
@@ -19131,7 +19136,7 @@
       </c>
     </row>
     <row r="58" spans="1:9" ht="28">
-      <c r="A58" s="85"/>
+      <c r="A58" s="83"/>
       <c r="B58" s="6" t="s">
         <v>85</v>
       </c>
@@ -19158,7 +19163,7 @@
       </c>
     </row>
     <row r="59" spans="1:9" ht="14">
-      <c r="A59" s="85"/>
+      <c r="A59" s="83"/>
       <c r="B59" s="6" t="s">
         <v>92</v>
       </c>
@@ -19168,7 +19173,7 @@
       <c r="D59" s="6" t="s">
         <v>1394</v>
       </c>
-      <c r="E59" s="86" t="s">
+      <c r="E59" s="76" t="s">
         <v>1653</v>
       </c>
       <c r="F59" s="9" t="s">
@@ -19185,7 +19190,7 @@
       </c>
     </row>
     <row r="60" spans="1:9" ht="70">
-      <c r="A60" s="85"/>
+      <c r="A60" s="83"/>
       <c r="B60" s="7"/>
       <c r="C60" s="6" t="s">
         <v>1398</v>
@@ -19193,7 +19198,7 @@
       <c r="D60" s="6" t="s">
         <v>1399</v>
       </c>
-      <c r="E60" s="86" t="s">
+      <c r="E60" s="76" t="s">
         <v>1654</v>
       </c>
       <c r="F60" s="9" t="s">
@@ -19210,7 +19215,7 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="14">
-      <c r="A61" s="83" t="s">
+      <c r="A61" s="86" t="s">
         <v>257</v>
       </c>
       <c r="B61" s="6" t="s">
@@ -19236,7 +19241,7 @@
       </c>
     </row>
     <row r="62" spans="1:9" ht="14">
-      <c r="A62" s="77"/>
+      <c r="A62" s="78"/>
       <c r="B62" s="7"/>
       <c r="C62" s="6" t="s">
         <v>1052</v>
@@ -19258,7 +19263,7 @@
       </c>
     </row>
     <row r="63" spans="1:9" ht="98">
-      <c r="A63" s="77"/>
+      <c r="A63" s="78"/>
       <c r="B63" s="6" t="s">
         <v>92</v>
       </c>
@@ -19282,7 +19287,7 @@
       </c>
     </row>
     <row r="64" spans="1:9" ht="14">
-      <c r="A64" s="77"/>
+      <c r="A64" s="78"/>
       <c r="B64" s="7"/>
       <c r="C64" s="6" t="s">
         <v>1060</v>
@@ -19304,7 +19309,7 @@
       </c>
     </row>
     <row r="65" spans="1:9" ht="98">
-      <c r="A65" s="77"/>
+      <c r="A65" s="78"/>
       <c r="B65" s="7"/>
       <c r="C65" s="6" t="s">
         <v>1062</v>
@@ -19326,7 +19331,7 @@
       </c>
     </row>
     <row r="66" spans="1:9" ht="14">
-      <c r="A66" s="77"/>
+      <c r="A66" s="78"/>
       <c r="B66" s="7"/>
       <c r="C66" s="6" t="s">
         <v>1068</v>
@@ -19348,7 +19353,7 @@
       </c>
     </row>
     <row r="67" spans="1:9" ht="84">
-      <c r="A67" s="77"/>
+      <c r="A67" s="78"/>
       <c r="B67" s="6" t="s">
         <v>85</v>
       </c>
@@ -19372,7 +19377,7 @@
       </c>
     </row>
     <row r="68" spans="1:9" ht="14">
-      <c r="A68" s="77"/>
+      <c r="A68" s="78"/>
       <c r="B68" s="7"/>
       <c r="C68" s="6" t="s">
         <v>1076</v>
@@ -19394,7 +19399,7 @@
       </c>
     </row>
     <row r="69" spans="1:9" ht="84">
-      <c r="A69" s="77"/>
+      <c r="A69" s="78"/>
       <c r="B69" s="7"/>
       <c r="C69" s="6" t="s">
         <v>1078</v>
@@ -19712,7 +19717,7 @@
       </c>
     </row>
     <row r="83" spans="1:9" ht="28">
-      <c r="A83" s="84" t="s">
+      <c r="A83" s="87" t="s">
         <v>371</v>
       </c>
       <c r="B83" s="7"/>
@@ -19736,7 +19741,7 @@
       </c>
     </row>
     <row r="84" spans="1:9" ht="28">
-      <c r="A84" s="77"/>
+      <c r="A84" s="78"/>
       <c r="B84" s="7"/>
       <c r="C84" s="6" t="s">
         <v>1164</v>
@@ -19758,7 +19763,7 @@
       </c>
     </row>
     <row r="85" spans="1:9" ht="28">
-      <c r="A85" s="77"/>
+      <c r="A85" s="78"/>
       <c r="B85" s="7"/>
       <c r="C85" s="6" t="s">
         <v>1170</v>
@@ -19780,7 +19785,7 @@
       </c>
     </row>
     <row r="86" spans="1:9" ht="56">
-      <c r="A86" s="77"/>
+      <c r="A86" s="78"/>
       <c r="B86" s="7"/>
       <c r="C86" s="6" t="s">
         <v>1176</v>
@@ -19802,7 +19807,7 @@
       </c>
     </row>
     <row r="87" spans="1:9" ht="28">
-      <c r="A87" s="77"/>
+      <c r="A87" s="78"/>
       <c r="B87" s="7"/>
       <c r="C87" s="6" t="s">
         <v>1182</v>
@@ -19824,7 +19829,7 @@
       </c>
     </row>
     <row r="88" spans="1:9" ht="42">
-      <c r="A88" s="77"/>
+      <c r="A88" s="78"/>
       <c r="B88" s="7"/>
       <c r="C88" s="6" t="s">
         <v>1188</v>
@@ -19846,7 +19851,7 @@
       </c>
     </row>
     <row r="89" spans="1:9" ht="28">
-      <c r="A89" s="77"/>
+      <c r="A89" s="78"/>
       <c r="B89" s="7"/>
       <c r="C89" s="6" t="s">
         <v>1194</v>
@@ -19868,7 +19873,7 @@
       </c>
     </row>
     <row r="90" spans="1:9" ht="42">
-      <c r="A90" s="77"/>
+      <c r="A90" s="78"/>
       <c r="B90" s="7"/>
       <c r="C90" s="6" t="s">
         <v>1200</v>
@@ -25672,7 +25677,7 @@
       <c r="I5" s="12"/>
     </row>
     <row r="6" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A6" s="84" t="s">
+      <c r="A6" s="87" t="s">
         <v>30</v>
       </c>
       <c r="B6" s="13" t="s">
@@ -25698,7 +25703,7 @@
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A7" s="77"/>
+      <c r="A7" s="78"/>
       <c r="B7" s="15" t="s">
         <v>35</v>
       </c>
@@ -25712,7 +25717,7 @@
       <c r="I7" s="12"/>
     </row>
     <row r="8" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A8" s="77"/>
+      <c r="A8" s="78"/>
       <c r="B8" s="15" t="s">
         <v>31</v>
       </c>
@@ -25736,7 +25741,7 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A9" s="77"/>
+      <c r="A9" s="78"/>
       <c r="B9" s="15" t="s">
         <v>35</v>
       </c>
@@ -25750,7 +25755,7 @@
       <c r="I9" s="12"/>
     </row>
     <row r="10" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A10" s="77"/>
+      <c r="A10" s="78"/>
       <c r="B10" s="15" t="s">
         <v>31</v>
       </c>
@@ -25774,7 +25779,7 @@
       </c>
     </row>
     <row r="11" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A11" s="77"/>
+      <c r="A11" s="78"/>
       <c r="B11" s="15" t="s">
         <v>40</v>
       </c>
@@ -25798,7 +25803,7 @@
       </c>
     </row>
     <row r="12" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A12" s="77"/>
+      <c r="A12" s="78"/>
       <c r="B12" s="15" t="s">
         <v>45</v>
       </c>
@@ -26000,7 +26005,7 @@
       </c>
     </row>
     <row r="21" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A21" s="83" t="s">
+      <c r="A21" s="86" t="s">
         <v>70</v>
       </c>
       <c r="B21" s="6" t="s">
@@ -26026,7 +26031,7 @@
       </c>
     </row>
     <row r="22" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A22" s="77"/>
+      <c r="A22" s="78"/>
       <c r="B22" s="7"/>
       <c r="C22" s="6" t="s">
         <v>1251</v>
@@ -26048,7 +26053,7 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A23" s="83" t="s">
+      <c r="A23" s="86" t="s">
         <v>84</v>
       </c>
       <c r="B23" s="6" t="s">
@@ -26074,7 +26079,7 @@
       </c>
     </row>
     <row r="24" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A24" s="77"/>
+      <c r="A24" s="78"/>
       <c r="B24" s="6" t="s">
         <v>92</v>
       </c>
@@ -26098,7 +26103,7 @@
       </c>
     </row>
     <row r="25" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A25" s="77"/>
+      <c r="A25" s="78"/>
       <c r="B25" s="7"/>
       <c r="C25" s="6" t="s">
         <v>1269</v>
@@ -26120,7 +26125,7 @@
       </c>
     </row>
     <row r="26" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A26" s="77"/>
+      <c r="A26" s="78"/>
       <c r="B26" s="6" t="s">
         <v>92</v>
       </c>
@@ -26144,7 +26149,7 @@
       </c>
     </row>
     <row r="27" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A27" s="77"/>
+      <c r="A27" s="78"/>
       <c r="B27" s="7"/>
       <c r="C27" s="6" t="s">
         <v>1281</v>
@@ -26166,7 +26171,7 @@
       </c>
     </row>
     <row r="28" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A28" s="77"/>
+      <c r="A28" s="78"/>
       <c r="B28" s="6" t="s">
         <v>92</v>
       </c>
@@ -26190,7 +26195,7 @@
       </c>
     </row>
     <row r="29" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A29" s="77"/>
+      <c r="A29" s="78"/>
       <c r="B29" s="7"/>
       <c r="C29" s="6" t="s">
         <v>1293</v>
@@ -26212,7 +26217,7 @@
       </c>
     </row>
     <row r="30" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A30" s="77"/>
+      <c r="A30" s="78"/>
       <c r="B30" s="6" t="s">
         <v>92</v>
       </c>
@@ -26236,7 +26241,7 @@
       </c>
     </row>
     <row r="31" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A31" s="77"/>
+      <c r="A31" s="78"/>
       <c r="B31" s="7"/>
       <c r="C31" s="6" t="s">
         <v>1305</v>
@@ -26258,7 +26263,7 @@
       </c>
     </row>
     <row r="32" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A32" s="83" t="s">
+      <c r="A32" s="86" t="s">
         <v>141</v>
       </c>
       <c r="B32" s="6" t="s">
@@ -26284,7 +26289,7 @@
       </c>
     </row>
     <row r="33" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A33" s="77"/>
+      <c r="A33" s="78"/>
       <c r="B33" s="7"/>
       <c r="C33" s="6" t="s">
         <v>1317</v>
@@ -26306,7 +26311,7 @@
       </c>
     </row>
     <row r="34" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A34" s="77"/>
+      <c r="A34" s="78"/>
       <c r="B34" s="6" t="s">
         <v>92</v>
       </c>
@@ -26330,7 +26335,7 @@
       </c>
     </row>
     <row r="35" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A35" s="77"/>
+      <c r="A35" s="78"/>
       <c r="B35" s="7"/>
       <c r="C35" s="6" t="s">
         <v>1329</v>
@@ -26352,7 +26357,7 @@
       </c>
     </row>
     <row r="36" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A36" s="77"/>
+      <c r="A36" s="78"/>
       <c r="B36" s="6" t="s">
         <v>92</v>
       </c>
@@ -26376,7 +26381,7 @@
       </c>
     </row>
     <row r="37" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A37" s="77"/>
+      <c r="A37" s="78"/>
       <c r="B37" s="7"/>
       <c r="C37" s="6" t="s">
         <v>1341</v>
@@ -26398,7 +26403,7 @@
       </c>
     </row>
     <row r="38" spans="1:9" ht="28">
-      <c r="A38" s="77"/>
+      <c r="A38" s="78"/>
       <c r="B38" s="6" t="s">
         <v>92</v>
       </c>
@@ -26422,7 +26427,7 @@
       </c>
     </row>
     <row r="39" spans="1:9" ht="84">
-      <c r="A39" s="77"/>
+      <c r="A39" s="78"/>
       <c r="B39" s="7"/>
       <c r="C39" s="6" t="s">
         <v>1353</v>
@@ -26444,7 +26449,7 @@
       </c>
     </row>
     <row r="40" spans="1:9" ht="28">
-      <c r="A40" s="77"/>
+      <c r="A40" s="78"/>
       <c r="B40" s="6" t="s">
         <v>92</v>
       </c>
@@ -26468,7 +26473,7 @@
       </c>
     </row>
     <row r="41" spans="1:9" ht="70">
-      <c r="A41" s="77"/>
+      <c r="A41" s="78"/>
       <c r="B41" s="7"/>
       <c r="C41" s="6" t="s">
         <v>1365</v>
@@ -26490,7 +26495,7 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="28">
-      <c r="A42" s="83" t="s">
+      <c r="A42" s="86" t="s">
         <v>202</v>
       </c>
       <c r="B42" s="6" t="s">
@@ -26516,7 +26521,7 @@
       </c>
     </row>
     <row r="43" spans="1:9" ht="14">
-      <c r="A43" s="77"/>
+      <c r="A43" s="78"/>
       <c r="B43" s="7"/>
       <c r="C43" s="6" t="s">
         <v>1377</v>
@@ -26538,7 +26543,7 @@
       </c>
     </row>
     <row r="44" spans="1:9" ht="28">
-      <c r="A44" s="77"/>
+      <c r="A44" s="78"/>
       <c r="B44" s="7"/>
       <c r="C44" s="6" t="s">
         <v>1378</v>
@@ -26560,7 +26565,7 @@
       </c>
     </row>
     <row r="45" spans="1:9" ht="28">
-      <c r="A45" s="77"/>
+      <c r="A45" s="78"/>
       <c r="B45" s="7"/>
       <c r="C45" s="6" t="s">
         <v>1380</v>
@@ -26582,7 +26587,7 @@
       </c>
     </row>
     <row r="46" spans="1:9" ht="42">
-      <c r="A46" s="77"/>
+      <c r="A46" s="78"/>
       <c r="B46" s="7"/>
       <c r="C46" s="6" t="s">
         <v>1382</v>
@@ -26604,7 +26609,7 @@
       </c>
     </row>
     <row r="47" spans="1:9" ht="28">
-      <c r="A47" s="77"/>
+      <c r="A47" s="78"/>
       <c r="B47" s="7"/>
       <c r="C47" s="6" t="s">
         <v>1384</v>
@@ -26626,7 +26631,7 @@
       </c>
     </row>
     <row r="48" spans="1:9" ht="14">
-      <c r="A48" s="77"/>
+      <c r="A48" s="78"/>
       <c r="B48" s="7"/>
       <c r="C48" s="6" t="s">
         <v>1389</v>
@@ -26648,7 +26653,7 @@
       </c>
     </row>
     <row r="49" spans="1:9" ht="28">
-      <c r="A49" s="85" t="s">
+      <c r="A49" s="83" t="s">
         <v>240</v>
       </c>
       <c r="B49" s="49" t="s">
@@ -26677,7 +26682,7 @@
       </c>
     </row>
     <row r="50" spans="1:9" ht="14">
-      <c r="A50" s="85"/>
+      <c r="A50" s="83"/>
       <c r="B50" s="49" t="s">
         <v>92</v>
       </c>
@@ -26704,7 +26709,7 @@
       </c>
     </row>
     <row r="51" spans="1:9" ht="70">
-      <c r="A51" s="85"/>
+      <c r="A51" s="83"/>
       <c r="B51" s="50"/>
       <c r="C51" s="49" t="s">
         <v>251</v>
@@ -26729,7 +26734,7 @@
       </c>
     </row>
     <row r="52" spans="1:9" ht="28">
-      <c r="A52" s="85"/>
+      <c r="A52" s="83"/>
       <c r="B52" s="6" t="s">
         <v>85</v>
       </c>
@@ -26756,7 +26761,7 @@
       </c>
     </row>
     <row r="53" spans="1:9" ht="14">
-      <c r="A53" s="85"/>
+      <c r="A53" s="83"/>
       <c r="B53" s="6" t="s">
         <v>92</v>
       </c>
@@ -26766,7 +26771,7 @@
       <c r="D53" s="6" t="s">
         <v>687</v>
       </c>
-      <c r="E53" s="86" t="s">
+      <c r="E53" s="76" t="s">
         <v>1649</v>
       </c>
       <c r="F53" s="9" t="s">
@@ -26783,7 +26788,7 @@
       </c>
     </row>
     <row r="54" spans="1:9" ht="56">
-      <c r="A54" s="85"/>
+      <c r="A54" s="83"/>
       <c r="B54" s="7"/>
       <c r="C54" s="6" t="s">
         <v>692</v>
@@ -26791,7 +26796,7 @@
       <c r="D54" s="16" t="s">
         <v>693</v>
       </c>
-      <c r="E54" s="86" t="s">
+      <c r="E54" s="76" t="s">
         <v>1650</v>
       </c>
       <c r="F54" s="9" t="s">
@@ -26808,7 +26813,7 @@
       </c>
     </row>
     <row r="55" spans="1:9" ht="28">
-      <c r="A55" s="85"/>
+      <c r="A55" s="83"/>
       <c r="B55" s="6" t="s">
         <v>85</v>
       </c>
@@ -26835,7 +26840,7 @@
       </c>
     </row>
     <row r="56" spans="1:9" ht="14">
-      <c r="A56" s="85"/>
+      <c r="A56" s="83"/>
       <c r="B56" s="6" t="s">
         <v>92</v>
       </c>
@@ -26845,7 +26850,7 @@
       <c r="D56" s="6" t="s">
         <v>1039</v>
       </c>
-      <c r="E56" s="86" t="s">
+      <c r="E56" s="76" t="s">
         <v>1651</v>
       </c>
       <c r="F56" s="9" t="s">
@@ -26862,7 +26867,7 @@
       </c>
     </row>
     <row r="57" spans="1:9" ht="70">
-      <c r="A57" s="85"/>
+      <c r="A57" s="83"/>
       <c r="B57" s="7"/>
       <c r="C57" s="6" t="s">
         <v>1044</v>
@@ -26870,7 +26875,7 @@
       <c r="D57" s="6" t="s">
         <v>1045</v>
       </c>
-      <c r="E57" s="86" t="s">
+      <c r="E57" s="76" t="s">
         <v>1652</v>
       </c>
       <c r="F57" s="9" t="s">
@@ -26887,7 +26892,7 @@
       </c>
     </row>
     <row r="58" spans="1:9" ht="28">
-      <c r="A58" s="85"/>
+      <c r="A58" s="83"/>
       <c r="B58" s="6" t="s">
         <v>85</v>
       </c>
@@ -26914,7 +26919,7 @@
       </c>
     </row>
     <row r="59" spans="1:9" ht="14">
-      <c r="A59" s="85"/>
+      <c r="A59" s="83"/>
       <c r="B59" s="6" t="s">
         <v>92</v>
       </c>
@@ -26924,7 +26929,7 @@
       <c r="D59" s="6" t="s">
         <v>1394</v>
       </c>
-      <c r="E59" s="86" t="s">
+      <c r="E59" s="76" t="s">
         <v>1653</v>
       </c>
       <c r="F59" s="9" t="s">
@@ -26941,7 +26946,7 @@
       </c>
     </row>
     <row r="60" spans="1:9" ht="70">
-      <c r="A60" s="85"/>
+      <c r="A60" s="83"/>
       <c r="B60" s="7"/>
       <c r="C60" s="6" t="s">
         <v>1398</v>
@@ -26949,7 +26954,7 @@
       <c r="D60" s="6" t="s">
         <v>1399</v>
       </c>
-      <c r="E60" s="86" t="s">
+      <c r="E60" s="76" t="s">
         <v>1654</v>
       </c>
       <c r="F60" s="9" t="s">
@@ -26966,7 +26971,7 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="14">
-      <c r="A61" s="83" t="s">
+      <c r="A61" s="86" t="s">
         <v>257</v>
       </c>
       <c r="B61" s="6" t="s">
@@ -26992,7 +26997,7 @@
       </c>
     </row>
     <row r="62" spans="1:9" ht="14">
-      <c r="A62" s="77"/>
+      <c r="A62" s="78"/>
       <c r="B62" s="7"/>
       <c r="C62" s="6" t="s">
         <v>1404</v>
@@ -27014,7 +27019,7 @@
       </c>
     </row>
     <row r="63" spans="1:9" ht="84">
-      <c r="A63" s="77"/>
+      <c r="A63" s="78"/>
       <c r="B63" s="6" t="s">
         <v>92</v>
       </c>
@@ -27038,7 +27043,7 @@
       </c>
     </row>
     <row r="64" spans="1:9" ht="14">
-      <c r="A64" s="77"/>
+      <c r="A64" s="78"/>
       <c r="B64" s="7"/>
       <c r="C64" s="6" t="s">
         <v>1412</v>
@@ -27060,7 +27065,7 @@
       </c>
     </row>
     <row r="65" spans="1:9" ht="70">
-      <c r="A65" s="77"/>
+      <c r="A65" s="78"/>
       <c r="B65" s="7"/>
       <c r="C65" s="6" t="s">
         <v>1414</v>
@@ -27082,7 +27087,7 @@
       </c>
     </row>
     <row r="66" spans="1:9" ht="14">
-      <c r="A66" s="77"/>
+      <c r="A66" s="78"/>
       <c r="B66" s="7"/>
       <c r="C66" s="6" t="s">
         <v>1420</v>
@@ -27104,7 +27109,7 @@
       </c>
     </row>
     <row r="67" spans="1:9" ht="70">
-      <c r="A67" s="77"/>
+      <c r="A67" s="78"/>
       <c r="B67" s="6" t="s">
         <v>85</v>
       </c>
@@ -27128,7 +27133,7 @@
       </c>
     </row>
     <row r="68" spans="1:9" ht="14">
-      <c r="A68" s="77"/>
+      <c r="A68" s="78"/>
       <c r="B68" s="7"/>
       <c r="C68" s="6" t="s">
         <v>1428</v>
@@ -27150,7 +27155,7 @@
       </c>
     </row>
     <row r="69" spans="1:9" ht="84">
-      <c r="A69" s="77"/>
+      <c r="A69" s="78"/>
       <c r="B69" s="7"/>
       <c r="C69" s="6" t="s">
         <v>1430</v>
@@ -27468,7 +27473,7 @@
       </c>
     </row>
     <row r="83" spans="1:9" ht="28">
-      <c r="A83" s="84" t="s">
+      <c r="A83" s="87" t="s">
         <v>371</v>
       </c>
       <c r="B83" s="7"/>
@@ -27492,7 +27497,7 @@
       </c>
     </row>
     <row r="84" spans="1:9" ht="56">
-      <c r="A84" s="77"/>
+      <c r="A84" s="78"/>
       <c r="B84" s="7"/>
       <c r="C84" s="6" t="s">
         <v>1515</v>
@@ -27514,7 +27519,7 @@
       </c>
     </row>
     <row r="85" spans="1:9" ht="28">
-      <c r="A85" s="77"/>
+      <c r="A85" s="78"/>
       <c r="B85" s="7"/>
       <c r="C85" s="6" t="s">
         <v>1521</v>
@@ -27536,7 +27541,7 @@
       </c>
     </row>
     <row r="86" spans="1:9" ht="56">
-      <c r="A86" s="77"/>
+      <c r="A86" s="78"/>
       <c r="B86" s="7"/>
       <c r="C86" s="6" t="s">
         <v>1527</v>
@@ -27558,7 +27563,7 @@
       </c>
     </row>
     <row r="87" spans="1:9" ht="28">
-      <c r="A87" s="77"/>
+      <c r="A87" s="78"/>
       <c r="B87" s="7"/>
       <c r="C87" s="6" t="s">
         <v>1533</v>
@@ -27580,7 +27585,7 @@
       </c>
     </row>
     <row r="88" spans="1:9" ht="42">
-      <c r="A88" s="77"/>
+      <c r="A88" s="78"/>
       <c r="B88" s="7"/>
       <c r="C88" s="6" t="s">
         <v>1539</v>
@@ -27602,7 +27607,7 @@
       </c>
     </row>
     <row r="89" spans="1:9" ht="42">
-      <c r="A89" s="77"/>
+      <c r="A89" s="78"/>
       <c r="B89" s="7"/>
       <c r="C89" s="6" t="s">
         <v>1545</v>
@@ -27624,7 +27629,7 @@
       </c>
     </row>
     <row r="90" spans="1:9" ht="56">
-      <c r="A90" s="77"/>
+      <c r="A90" s="78"/>
       <c r="B90" s="7"/>
       <c r="C90" s="6" t="s">
         <v>1551</v>

--- a/cms/app/content/faceswap-content.xlsx
+++ b/cms/app/content/faceswap-content.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shawaiz/git/pixel-morph/cms/app/content/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA352B7F-958C-FC4C-A947-A2842422D6AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B7B526E-806B-CA42-9ADA-B4054E47AF3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="25600" windowHeight="13720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="25600" windowHeight="13660" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="faceswap" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2614" uniqueCount="1657">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2703" uniqueCount="1657">
   <si>
     <t>Overview</t>
   </si>
@@ -9900,8 +9900,19 @@
     </row>
   </sheetData>
   <mergeCells count="150">
-    <mergeCell ref="R26:T26"/>
-    <mergeCell ref="S16:T16"/>
+    <mergeCell ref="M24:O24"/>
+    <mergeCell ref="R24:T24"/>
+    <mergeCell ref="M25:O25"/>
+    <mergeCell ref="R25:T25"/>
+    <mergeCell ref="R22:T22"/>
+    <mergeCell ref="S23:T23"/>
+    <mergeCell ref="N15:O15"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="M11:O11"/>
+    <mergeCell ref="R11:T11"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="S17:T17"/>
+    <mergeCell ref="N18:P18"/>
     <mergeCell ref="S21:T21"/>
     <mergeCell ref="M10:O10"/>
     <mergeCell ref="R10:T10"/>
@@ -9911,11 +9922,6 @@
     <mergeCell ref="R8:T8"/>
     <mergeCell ref="M9:N9"/>
     <mergeCell ref="R9:S9"/>
-    <mergeCell ref="M24:O24"/>
-    <mergeCell ref="R24:T24"/>
-    <mergeCell ref="M25:O25"/>
-    <mergeCell ref="R25:T25"/>
-    <mergeCell ref="A50:A61"/>
     <mergeCell ref="A85:A91"/>
     <mergeCell ref="N2:P2"/>
     <mergeCell ref="S2:T2"/>
@@ -9939,11 +9945,7 @@
     <mergeCell ref="M33:O33"/>
     <mergeCell ref="S5:T5"/>
     <mergeCell ref="S6:T6"/>
-    <mergeCell ref="R22:T22"/>
-    <mergeCell ref="S23:T23"/>
-    <mergeCell ref="N15:O15"/>
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="M87:O87"/>
+    <mergeCell ref="R26:T26"/>
     <mergeCell ref="M88:O88"/>
     <mergeCell ref="M89:O89"/>
     <mergeCell ref="R90:T90"/>
@@ -9963,11 +9965,11 @@
     <mergeCell ref="M44:O44"/>
     <mergeCell ref="M39:O39"/>
     <mergeCell ref="M38:O38"/>
-    <mergeCell ref="M11:O11"/>
-    <mergeCell ref="R11:T11"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="S17:T17"/>
-    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="R34:T34"/>
+    <mergeCell ref="R35:T35"/>
+    <mergeCell ref="R39:T39"/>
+    <mergeCell ref="M40:O40"/>
+    <mergeCell ref="A50:A61"/>
     <mergeCell ref="S18:T18"/>
     <mergeCell ref="N19:P19"/>
     <mergeCell ref="S19:T19"/>
@@ -9978,6 +9980,7 @@
     <mergeCell ref="N14:P14"/>
     <mergeCell ref="S14:T14"/>
     <mergeCell ref="S15:T15"/>
+    <mergeCell ref="S16:T16"/>
     <mergeCell ref="R91:T91"/>
     <mergeCell ref="S75:T75"/>
     <mergeCell ref="S76:T76"/>
@@ -10001,10 +10004,7 @@
     <mergeCell ref="S83:T83"/>
     <mergeCell ref="S84:T84"/>
     <mergeCell ref="M91:O91"/>
-    <mergeCell ref="R34:T34"/>
-    <mergeCell ref="R35:T35"/>
-    <mergeCell ref="R39:T39"/>
-    <mergeCell ref="M40:O40"/>
+    <mergeCell ref="M87:O87"/>
     <mergeCell ref="R40:T40"/>
     <mergeCell ref="M41:O41"/>
     <mergeCell ref="R41:T41"/>
@@ -10079,31 +10079,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
+      <c r="F1" s="48" t="s">
+        <v>1557</v>
+      </c>
+      <c r="G1" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="48" t="s">
         <v>8</v>
       </c>
     </row>
@@ -10118,6 +10118,9 @@
       <c r="D2" s="6" t="s">
         <v>478</v>
       </c>
+      <c r="E2" s="51" t="s">
+        <v>414</v>
+      </c>
       <c r="F2" s="9" t="s">
         <v>479</v>
       </c>
@@ -10142,6 +10145,9 @@
       <c r="D3" s="16" t="s">
         <v>484</v>
       </c>
+      <c r="E3" s="51" t="s">
+        <v>415</v>
+      </c>
       <c r="F3" s="9" t="s">
         <v>485</v>
       </c>
@@ -10165,6 +10171,9 @@
       </c>
       <c r="D4" s="6" t="s">
         <v>490</v>
+      </c>
+      <c r="E4" s="51" t="s">
+        <v>416</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>491</v>
@@ -10186,6 +10195,7 @@
         <v>495</v>
       </c>
       <c r="D5" s="26"/>
+      <c r="E5" s="51"/>
       <c r="F5" s="12"/>
       <c r="G5" s="32"/>
       <c r="H5" s="12"/>
@@ -10204,6 +10214,9 @@
       <c r="D6" s="6" t="s">
         <v>478</v>
       </c>
+      <c r="E6" s="51" t="s">
+        <v>417</v>
+      </c>
       <c r="F6" s="9" t="s">
         <v>479</v>
       </c>
@@ -10226,6 +10239,7 @@
         <v>498</v>
       </c>
       <c r="D7" s="6"/>
+      <c r="E7" s="51"/>
       <c r="F7" s="12"/>
       <c r="G7" s="32"/>
       <c r="H7" s="12"/>
@@ -10242,6 +10256,9 @@
       <c r="D8" s="6" t="s">
         <v>478</v>
       </c>
+      <c r="E8" s="51" t="s">
+        <v>418</v>
+      </c>
       <c r="F8" s="9" t="s">
         <v>479</v>
       </c>
@@ -10264,6 +10281,7 @@
         <v>500</v>
       </c>
       <c r="D9" s="6"/>
+      <c r="E9" s="51"/>
       <c r="F9" s="12"/>
       <c r="G9" s="32"/>
       <c r="H9" s="12"/>
@@ -10280,6 +10298,9 @@
       <c r="D10" s="6" t="s">
         <v>478</v>
       </c>
+      <c r="E10" s="51" t="s">
+        <v>418</v>
+      </c>
       <c r="F10" s="9" t="s">
         <v>479</v>
       </c>
@@ -10304,6 +10325,9 @@
       <c r="D11" s="16" t="s">
         <v>484</v>
       </c>
+      <c r="E11" s="51" t="s">
+        <v>419</v>
+      </c>
       <c r="F11" s="9" t="s">
         <v>485</v>
       </c>
@@ -10326,6 +10350,7 @@
         <v>504</v>
       </c>
       <c r="D12" s="17"/>
+      <c r="E12" s="64"/>
       <c r="F12" s="12"/>
       <c r="G12" s="32"/>
       <c r="H12" s="12"/>
@@ -10344,6 +10369,9 @@
       <c r="D13" s="6" t="s">
         <v>478</v>
       </c>
+      <c r="E13" s="51" t="s">
+        <v>418</v>
+      </c>
       <c r="F13" s="9" t="s">
         <v>479</v>
       </c>
@@ -10370,6 +10398,9 @@
       <c r="D14" s="16" t="s">
         <v>484</v>
       </c>
+      <c r="E14" s="51" t="s">
+        <v>419</v>
+      </c>
       <c r="F14" s="9" t="s">
         <v>485</v>
       </c>
@@ -10394,6 +10425,7 @@
         <v>507</v>
       </c>
       <c r="D15" s="6"/>
+      <c r="E15" s="51"/>
       <c r="F15" s="12"/>
       <c r="G15" s="32"/>
       <c r="H15" s="12"/>
@@ -10409,11 +10441,24 @@
       <c r="C16" s="11" t="s">
         <v>508</v>
       </c>
-      <c r="D16" s="6"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="32"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="12"/>
+      <c r="D16" s="16" t="s">
+        <v>484</v>
+      </c>
+      <c r="E16" s="51" t="s">
+        <v>416</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>485</v>
+      </c>
+      <c r="G16" s="27" t="s">
+        <v>486</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>503</v>
+      </c>
     </row>
     <row r="17" spans="1:9" ht="15.75" customHeight="1">
       <c r="A17" s="15" t="s">
@@ -10425,21 +10470,7 @@
       <c r="C17" s="11" t="s">
         <v>509</v>
       </c>
-      <c r="D17" s="16" t="s">
-        <v>484</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>485</v>
-      </c>
-      <c r="G17" s="27" t="s">
-        <v>486</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>510</v>
-      </c>
-      <c r="I17" s="9" t="s">
-        <v>503</v>
-      </c>
+      <c r="E17" s="64"/>
     </row>
     <row r="18" spans="1:9" ht="15.75" customHeight="1">
       <c r="A18" s="15" t="s">
@@ -10454,6 +10485,9 @@
       <c r="D18" s="6" t="s">
         <v>478</v>
       </c>
+      <c r="E18" s="51" t="s">
+        <v>418</v>
+      </c>
       <c r="F18" s="9" t="s">
         <v>479</v>
       </c>
@@ -10480,6 +10514,9 @@
       <c r="D19" s="16" t="s">
         <v>484</v>
       </c>
+      <c r="E19" s="51" t="s">
+        <v>420</v>
+      </c>
       <c r="F19" s="9" t="s">
         <v>485</v>
       </c>
@@ -10506,6 +10543,9 @@
       <c r="D20" s="11" t="s">
         <v>490</v>
       </c>
+      <c r="E20" s="51" t="s">
+        <v>421</v>
+      </c>
       <c r="F20" s="9" t="s">
         <v>491</v>
       </c>
@@ -10531,6 +10571,9 @@
       </c>
       <c r="D21" s="21" t="s">
         <v>515</v>
+      </c>
+      <c r="E21" s="66" t="s">
+        <v>1656</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>516</v>
@@ -10554,6 +10597,9 @@
       <c r="D22" s="6" t="s">
         <v>521</v>
       </c>
+      <c r="E22" s="51" t="s">
+        <v>422</v>
+      </c>
       <c r="F22" s="9" t="s">
         <v>522</v>
       </c>
@@ -10579,6 +10625,9 @@
       </c>
       <c r="D23" s="33" t="s">
         <v>527</v>
+      </c>
+      <c r="E23" s="47" t="s">
+        <v>423</v>
       </c>
       <c r="F23" s="22" t="s">
         <v>528</v>
@@ -10603,6 +10652,9 @@
       </c>
       <c r="D24" s="33" t="s">
         <v>533</v>
+      </c>
+      <c r="E24" s="47" t="s">
+        <v>424</v>
       </c>
       <c r="F24" s="22" t="s">
         <v>534</v>
@@ -10626,6 +10678,9 @@
       <c r="D25" s="16" t="s">
         <v>539</v>
       </c>
+      <c r="E25" s="51" t="s">
+        <v>425</v>
+      </c>
       <c r="F25" s="9" t="s">
         <v>540</v>
       </c>
@@ -10649,6 +10704,9 @@
       </c>
       <c r="D26" s="16" t="s">
         <v>545</v>
+      </c>
+      <c r="E26" s="47" t="s">
+        <v>426</v>
       </c>
       <c r="F26" s="9" t="s">
         <v>546</v>
@@ -10672,6 +10730,9 @@
       <c r="D27" s="6" t="s">
         <v>551</v>
       </c>
+      <c r="E27" s="51" t="s">
+        <v>427</v>
+      </c>
       <c r="F27" s="9" t="s">
         <v>552</v>
       </c>
@@ -10695,6 +10756,9 @@
       </c>
       <c r="D28" s="21" t="s">
         <v>557</v>
+      </c>
+      <c r="E28" s="47" t="s">
+        <v>428</v>
       </c>
       <c r="F28" s="22" t="s">
         <v>558</v>
@@ -10718,6 +10782,9 @@
       <c r="D29" s="16" t="s">
         <v>563</v>
       </c>
+      <c r="E29" s="51" t="s">
+        <v>429</v>
+      </c>
       <c r="F29" s="9" t="s">
         <v>564</v>
       </c>
@@ -10741,6 +10808,9 @@
       </c>
       <c r="D30" s="21" t="s">
         <v>569</v>
+      </c>
+      <c r="E30" s="47" t="s">
+        <v>430</v>
       </c>
       <c r="F30" s="22" t="s">
         <v>570</v>
@@ -10764,6 +10834,9 @@
       <c r="D31" s="16" t="s">
         <v>575</v>
       </c>
+      <c r="E31" s="51" t="s">
+        <v>431</v>
+      </c>
       <c r="F31" s="9" t="s">
         <v>576</v>
       </c>
@@ -10789,6 +10862,9 @@
       </c>
       <c r="D32" s="21" t="s">
         <v>581</v>
+      </c>
+      <c r="E32" s="47" t="s">
+        <v>432</v>
       </c>
       <c r="F32" s="22" t="s">
         <v>582</v>
@@ -10812,6 +10888,9 @@
       <c r="D33" s="16" t="s">
         <v>587</v>
       </c>
+      <c r="E33" s="51" t="s">
+        <v>433</v>
+      </c>
       <c r="F33" s="9" t="s">
         <v>588</v>
       </c>
@@ -10835,6 +10914,9 @@
       </c>
       <c r="D34" s="24" t="s">
         <v>593</v>
+      </c>
+      <c r="E34" s="47" t="s">
+        <v>434</v>
       </c>
       <c r="F34" s="9" t="s">
         <v>594</v>
@@ -10858,6 +10940,9 @@
       <c r="D35" s="6" t="s">
         <v>599</v>
       </c>
+      <c r="E35" s="51" t="s">
+        <v>435</v>
+      </c>
       <c r="F35" s="9" t="s">
         <v>600</v>
       </c>
@@ -10881,6 +10966,9 @@
       </c>
       <c r="D36" s="24" t="s">
         <v>605</v>
+      </c>
+      <c r="E36" s="47" t="s">
+        <v>436</v>
       </c>
       <c r="F36" s="9" t="s">
         <v>606</v>
@@ -10904,6 +10992,9 @@
       <c r="D37" s="16" t="s">
         <v>611</v>
       </c>
+      <c r="E37" s="51" t="s">
+        <v>437</v>
+      </c>
       <c r="F37" s="9" t="s">
         <v>612</v>
       </c>
@@ -10927,6 +11018,9 @@
       </c>
       <c r="D38" s="24" t="s">
         <v>617</v>
+      </c>
+      <c r="E38" s="47" t="s">
+        <v>438</v>
       </c>
       <c r="F38" s="9" t="s">
         <v>618</v>
@@ -10950,6 +11044,9 @@
       <c r="D39" s="16" t="s">
         <v>623</v>
       </c>
+      <c r="E39" s="51" t="s">
+        <v>439</v>
+      </c>
       <c r="F39" s="9" t="s">
         <v>624</v>
       </c>
@@ -10973,6 +11070,9 @@
       </c>
       <c r="D40" s="24" t="s">
         <v>629</v>
+      </c>
+      <c r="E40" s="47" t="s">
+        <v>440</v>
       </c>
       <c r="F40" s="9" t="s">
         <v>630</v>
@@ -10996,6 +11096,9 @@
       <c r="D41" s="16" t="s">
         <v>635</v>
       </c>
+      <c r="E41" s="51" t="s">
+        <v>441</v>
+      </c>
       <c r="F41" s="9" t="s">
         <v>636</v>
       </c>
@@ -11021,6 +11124,9 @@
       </c>
       <c r="D42" s="16" t="s">
         <v>641</v>
+      </c>
+      <c r="E42" s="47" t="s">
+        <v>442</v>
       </c>
       <c r="F42" s="9" t="s">
         <v>642</v>
@@ -11044,6 +11150,9 @@
       <c r="D43" s="16" t="s">
         <v>647</v>
       </c>
+      <c r="E43" s="51" t="s">
+        <v>443</v>
+      </c>
       <c r="F43" s="9" t="s">
         <v>648</v>
       </c>
@@ -11066,6 +11175,9 @@
       <c r="D44" s="16" t="s">
         <v>653</v>
       </c>
+      <c r="E44" s="51" t="s">
+        <v>444</v>
+      </c>
       <c r="F44" s="9" t="s">
         <v>654</v>
       </c>
@@ -11088,6 +11200,9 @@
       <c r="D45" s="16" t="s">
         <v>659</v>
       </c>
+      <c r="E45" s="47" t="s">
+        <v>443</v>
+      </c>
       <c r="F45" s="9" t="s">
         <v>660</v>
       </c>
@@ -11110,6 +11225,9 @@
       <c r="D46" s="16" t="s">
         <v>665</v>
       </c>
+      <c r="E46" s="51" t="s">
+        <v>445</v>
+      </c>
       <c r="F46" s="9" t="s">
         <v>666</v>
       </c>
@@ -11132,6 +11250,9 @@
       <c r="D47" s="16" t="s">
         <v>671</v>
       </c>
+      <c r="E47" s="51" t="s">
+        <v>446</v>
+      </c>
       <c r="F47" s="9" t="s">
         <v>672</v>
       </c>
@@ -11154,6 +11275,7 @@
       <c r="D48" s="16" t="s">
         <v>677</v>
       </c>
+      <c r="E48" s="51"/>
       <c r="F48" s="9" t="s">
         <v>678</v>
       </c>
@@ -11181,7 +11303,7 @@
         <v>242</v>
       </c>
       <c r="E49" s="51" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F49" s="52" t="s">
         <v>243</v>
@@ -11208,7 +11330,7 @@
         <v>25</v>
       </c>
       <c r="E50" s="51" t="s">
-        <v>421</v>
+        <v>448</v>
       </c>
       <c r="F50" s="52" t="s">
         <v>25</v>
@@ -11233,7 +11355,7 @@
         <v>252</v>
       </c>
       <c r="E51" s="51" t="s">
-        <v>449</v>
+        <v>421</v>
       </c>
       <c r="F51" s="52" t="s">
         <v>253</v>
@@ -11260,7 +11382,7 @@
         <v>242</v>
       </c>
       <c r="E52" s="51" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F52" s="9" t="s">
         <v>683</v>
@@ -11286,8 +11408,8 @@
       <c r="D53" s="6" t="s">
         <v>687</v>
       </c>
-      <c r="E53" s="76" t="s">
-        <v>1649</v>
+      <c r="E53" s="51" t="s">
+        <v>448</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>688</v>
@@ -11312,7 +11434,7 @@
         <v>693</v>
       </c>
       <c r="E54" s="76" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="F54" s="9" t="s">
         <v>694</v>
@@ -11338,8 +11460,8 @@
       <c r="D55" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="E55" s="51" t="s">
-        <v>448</v>
+      <c r="E55" s="76" t="s">
+        <v>1650</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>683</v>
@@ -11365,8 +11487,8 @@
       <c r="D56" s="6" t="s">
         <v>1039</v>
       </c>
-      <c r="E56" s="76" t="s">
-        <v>1651</v>
+      <c r="E56" s="51" t="s">
+        <v>448</v>
       </c>
       <c r="F56" s="9" t="s">
         <v>1040</v>
@@ -11391,7 +11513,7 @@
         <v>1045</v>
       </c>
       <c r="E57" s="76" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>1046</v>
@@ -11417,8 +11539,8 @@
       <c r="D58" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="E58" s="51" t="s">
-        <v>448</v>
+      <c r="E58" s="76" t="s">
+        <v>1652</v>
       </c>
       <c r="F58" s="9" t="s">
         <v>1391</v>
@@ -11444,8 +11566,8 @@
       <c r="D59" s="6" t="s">
         <v>1394</v>
       </c>
-      <c r="E59" s="76" t="s">
-        <v>1653</v>
+      <c r="E59" s="51" t="s">
+        <v>448</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>1395</v>
@@ -11470,7 +11592,7 @@
         <v>1399</v>
       </c>
       <c r="E60" s="76" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="F60" s="9" t="s">
         <v>1400</v>
@@ -11497,6 +11619,9 @@
       </c>
       <c r="D61" s="21" t="s">
         <v>699</v>
+      </c>
+      <c r="E61" s="76" t="s">
+        <v>1654</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>700</v>
@@ -11520,6 +11645,9 @@
       <c r="D62" s="11" t="s">
         <v>705</v>
       </c>
+      <c r="E62" s="76" t="s">
+        <v>1655</v>
+      </c>
       <c r="F62" s="9" t="s">
         <v>705</v>
       </c>
@@ -11543,6 +11671,9 @@
       </c>
       <c r="D63" s="16" t="s">
         <v>707</v>
+      </c>
+      <c r="E63" s="51" t="s">
+        <v>450</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>708</v>
@@ -11566,6 +11697,9 @@
       <c r="D64" s="16" t="s">
         <v>713</v>
       </c>
+      <c r="E64" s="51" t="s">
+        <v>451</v>
+      </c>
       <c r="F64" s="9" t="s">
         <v>713</v>
       </c>
@@ -11588,6 +11722,9 @@
       <c r="D65" s="16" t="s">
         <v>715</v>
       </c>
+      <c r="E65" s="51" t="s">
+        <v>452</v>
+      </c>
       <c r="F65" s="9" t="s">
         <v>716</v>
       </c>
@@ -11610,6 +11747,9 @@
       <c r="D66" s="16" t="s">
         <v>721</v>
       </c>
+      <c r="E66" s="51" t="s">
+        <v>453</v>
+      </c>
       <c r="F66" s="9" t="s">
         <v>721</v>
       </c>
@@ -11633,6 +11773,9 @@
       </c>
       <c r="D67" s="16" t="s">
         <v>723</v>
+      </c>
+      <c r="E67" s="51" t="s">
+        <v>454</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>724</v>
@@ -11656,6 +11799,9 @@
       <c r="D68" s="11" t="s">
         <v>729</v>
       </c>
+      <c r="E68" s="51" t="s">
+        <v>455</v>
+      </c>
       <c r="F68" s="9" t="s">
         <v>729</v>
       </c>
@@ -11678,6 +11824,9 @@
       <c r="D69" s="6" t="s">
         <v>731</v>
       </c>
+      <c r="E69" s="51" t="s">
+        <v>456</v>
+      </c>
       <c r="F69" s="9" t="s">
         <v>732</v>
       </c>
@@ -11700,6 +11849,9 @@
         <v>736</v>
       </c>
       <c r="D70" s="21" t="s">
+        <v>737</v>
+      </c>
+      <c r="E70" s="21" t="s">
         <v>737</v>
       </c>
       <c r="F70" s="9" t="s">
@@ -11724,6 +11876,9 @@
       <c r="D71" s="6" t="s">
         <v>741</v>
       </c>
+      <c r="E71" s="51" t="s">
+        <v>457</v>
+      </c>
       <c r="F71" s="9" t="s">
         <v>742</v>
       </c>
@@ -11746,6 +11901,9 @@
       <c r="D72" s="16" t="s">
         <v>747</v>
       </c>
+      <c r="E72" s="51" t="s">
+        <v>458</v>
+      </c>
       <c r="F72" s="9" t="s">
         <v>748</v>
       </c>
@@ -11768,6 +11926,9 @@
       <c r="D73" s="16" t="s">
         <v>752</v>
       </c>
+      <c r="E73" s="51" t="s">
+        <v>459</v>
+      </c>
       <c r="F73" s="9" t="s">
         <v>753</v>
       </c>
@@ -11790,6 +11951,9 @@
       <c r="D74" s="16" t="s">
         <v>757</v>
       </c>
+      <c r="E74" s="51" t="s">
+        <v>460</v>
+      </c>
       <c r="F74" s="9" t="s">
         <v>758</v>
       </c>
@@ -11812,6 +11976,9 @@
       <c r="D75" s="16" t="s">
         <v>762</v>
       </c>
+      <c r="E75" s="51" t="s">
+        <v>461</v>
+      </c>
       <c r="F75" s="9" t="s">
         <v>763</v>
       </c>
@@ -11836,6 +12003,9 @@
       <c r="D76" s="16" t="s">
         <v>767</v>
       </c>
+      <c r="E76" s="51" t="s">
+        <v>462</v>
+      </c>
       <c r="F76" s="9" t="s">
         <v>768</v>
       </c>
@@ -11859,6 +12029,9 @@
       </c>
       <c r="D77" s="16" t="s">
         <v>772</v>
+      </c>
+      <c r="E77" s="51" t="s">
+        <v>463</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>773</v>
@@ -11882,6 +12055,9 @@
       <c r="D78" s="6" t="s">
         <v>777</v>
       </c>
+      <c r="E78" s="51" t="s">
+        <v>464</v>
+      </c>
       <c r="F78" s="9" t="s">
         <v>778</v>
       </c>
@@ -11905,6 +12081,9 @@
       </c>
       <c r="D79" s="16" t="s">
         <v>782</v>
+      </c>
+      <c r="E79" s="51" t="s">
+        <v>465</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>783</v>
@@ -11928,6 +12107,9 @@
       <c r="D80" s="16" t="s">
         <v>787</v>
       </c>
+      <c r="E80" s="51" t="s">
+        <v>466</v>
+      </c>
       <c r="F80" s="9" t="s">
         <v>788</v>
       </c>
@@ -11951,6 +12133,9 @@
       </c>
       <c r="D81" s="16" t="s">
         <v>792</v>
+      </c>
+      <c r="E81" s="51" t="s">
+        <v>467</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>793</v>
@@ -11974,6 +12159,9 @@
       <c r="D82" s="16" t="s">
         <v>797</v>
       </c>
+      <c r="E82" s="51" t="s">
+        <v>468</v>
+      </c>
       <c r="F82" s="9" t="s">
         <v>798</v>
       </c>
@@ -11997,6 +12185,9 @@
       </c>
       <c r="D83" s="6" t="s">
         <v>802</v>
+      </c>
+      <c r="E83" s="51" t="s">
+        <v>469</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>803</v>
@@ -12020,6 +12211,9 @@
       <c r="D84" s="16" t="s">
         <v>807</v>
       </c>
+      <c r="E84" s="51" t="s">
+        <v>470</v>
+      </c>
       <c r="F84" s="9" t="s">
         <v>808</v>
       </c>
@@ -12042,6 +12236,9 @@
       <c r="D85" s="16" t="s">
         <v>812</v>
       </c>
+      <c r="E85" s="51" t="s">
+        <v>471</v>
+      </c>
       <c r="F85" s="9" t="s">
         <v>813</v>
       </c>
@@ -12064,6 +12261,9 @@
       <c r="D86" s="16" t="s">
         <v>817</v>
       </c>
+      <c r="E86" s="51" t="s">
+        <v>472</v>
+      </c>
       <c r="F86" s="9" t="s">
         <v>818</v>
       </c>
@@ -12086,6 +12286,9 @@
       <c r="D87" s="16" t="s">
         <v>822</v>
       </c>
+      <c r="E87" s="51" t="s">
+        <v>473</v>
+      </c>
       <c r="F87" s="9" t="s">
         <v>823</v>
       </c>
@@ -12108,6 +12311,9 @@
       <c r="D88" s="16" t="s">
         <v>827</v>
       </c>
+      <c r="E88" s="51" t="s">
+        <v>474</v>
+      </c>
       <c r="F88" s="9" t="s">
         <v>828</v>
       </c>
@@ -12130,6 +12336,9 @@
       <c r="D89" s="16" t="s">
         <v>832</v>
       </c>
+      <c r="E89" s="51" t="s">
+        <v>475</v>
+      </c>
       <c r="F89" s="9" t="s">
         <v>404</v>
       </c>
@@ -12152,6 +12361,9 @@
       <c r="D90" s="16" t="s">
         <v>835</v>
       </c>
+      <c r="E90" s="51" t="s">
+        <v>476</v>
+      </c>
       <c r="F90" s="9" t="s">
         <v>836</v>
       </c>
@@ -12165,7 +12377,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="14">
+    <row r="91" spans="1:9" ht="28">
       <c r="A91" s="62" t="s">
         <v>1630</v>
       </c>
@@ -12176,8 +12388,8 @@
       <c r="D91" s="62" t="s">
         <v>1566</v>
       </c>
-      <c r="E91" s="73" t="s">
-        <v>1568</v>
+      <c r="E91" s="52" t="s">
+        <v>1570</v>
       </c>
       <c r="F91" s="52" t="s">
         <v>1570</v>
@@ -12202,7 +12414,7 @@
         <v>1567</v>
       </c>
       <c r="E92" s="74" t="s">
-        <v>1569</v>
+        <v>1571</v>
       </c>
       <c r="F92" s="74" t="s">
         <v>1571</v>
@@ -12217,7 +12429,7 @@
         <v>1577</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="14">
+    <row r="93" spans="1:9" ht="28">
       <c r="A93" s="62"/>
       <c r="B93" s="62"/>
       <c r="C93" s="49" t="s">
@@ -12226,8 +12438,8 @@
       <c r="D93" s="62" t="s">
         <v>1588</v>
       </c>
-      <c r="E93" s="73" t="s">
-        <v>1578</v>
+      <c r="E93" s="52" t="s">
+        <v>1580</v>
       </c>
       <c r="F93" s="52" t="s">
         <v>1580</v>
@@ -12252,7 +12464,7 @@
         <v>1587</v>
       </c>
       <c r="E94" s="74" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="F94" s="74" t="s">
         <v>1581</v>
@@ -12267,7 +12479,7 @@
         <v>1601</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="14">
+    <row r="95" spans="1:9" ht="28">
       <c r="A95" s="62"/>
       <c r="B95" s="62"/>
       <c r="C95" s="49" t="s">
@@ -12276,8 +12488,8 @@
       <c r="D95" s="62" t="s">
         <v>1589</v>
       </c>
-      <c r="E95" s="75" t="s">
-        <v>1591</v>
+      <c r="E95" s="62" t="s">
+        <v>1592</v>
       </c>
       <c r="F95" s="62" t="s">
         <v>1592</v>
@@ -12302,7 +12514,7 @@
         <v>1590</v>
       </c>
       <c r="E96" s="74" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="F96" s="74" t="s">
         <v>1599</v>
@@ -12317,193 +12529,313 @@
         <v>1596</v>
       </c>
     </row>
-    <row r="97" spans="1:4" ht="13">
-      <c r="A97" s="16"/>
-      <c r="B97" s="16"/>
-      <c r="C97" s="16"/>
-      <c r="D97" s="16"/>
-    </row>
-    <row r="98" spans="1:4" ht="13">
-      <c r="A98" s="16"/>
-      <c r="B98" s="16"/>
-      <c r="C98" s="16"/>
-      <c r="D98" s="16"/>
-    </row>
-    <row r="99" spans="1:4" ht="13">
-      <c r="A99" s="16"/>
-      <c r="B99" s="16"/>
-      <c r="C99" s="16"/>
-      <c r="D99" s="16"/>
-    </row>
-    <row r="100" spans="1:4" ht="13">
-      <c r="A100" s="16"/>
-      <c r="B100" s="16"/>
-      <c r="C100" s="16"/>
-      <c r="D100" s="16"/>
-    </row>
-    <row r="101" spans="1:4" ht="13">
-      <c r="A101" s="16"/>
-      <c r="B101" s="16"/>
-      <c r="C101" s="16"/>
-      <c r="D101" s="16"/>
-    </row>
-    <row r="102" spans="1:4" ht="13">
+    <row r="97" spans="1:9" ht="98">
+      <c r="A97" s="62" t="s">
+        <v>1623</v>
+      </c>
+      <c r="B97" s="62" t="s">
+        <v>1624</v>
+      </c>
+      <c r="C97" s="49" t="s">
+        <v>1608</v>
+      </c>
+      <c r="D97" s="62" t="s">
+        <v>1604</v>
+      </c>
+      <c r="E97" s="62" t="s">
+        <v>1603</v>
+      </c>
+      <c r="F97" s="62" t="s">
+        <v>1603</v>
+      </c>
+      <c r="G97" s="62" t="s">
+        <v>1605</v>
+      </c>
+      <c r="H97" s="62" t="s">
+        <v>1606</v>
+      </c>
+      <c r="I97" s="62" t="s">
+        <v>1607</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="28">
+      <c r="A98" s="62"/>
+      <c r="B98" s="62"/>
+      <c r="C98" s="49" t="s">
+        <v>1564</v>
+      </c>
+      <c r="D98" s="62" t="s">
+        <v>1616</v>
+      </c>
+      <c r="E98" s="74" t="s">
+        <v>1618</v>
+      </c>
+      <c r="F98" s="74" t="s">
+        <v>1618</v>
+      </c>
+      <c r="G98" s="74" t="s">
+        <v>1619</v>
+      </c>
+      <c r="H98" s="74" t="s">
+        <v>1620</v>
+      </c>
+      <c r="I98" s="74" t="s">
+        <v>1621</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="84">
+      <c r="A99" s="62"/>
+      <c r="B99" s="62"/>
+      <c r="C99" s="49" t="s">
+        <v>1609</v>
+      </c>
+      <c r="D99" s="62" t="s">
+        <v>1610</v>
+      </c>
+      <c r="E99" s="74" t="s">
+        <v>1612</v>
+      </c>
+      <c r="F99" s="74" t="s">
+        <v>1612</v>
+      </c>
+      <c r="G99" s="74" t="s">
+        <v>1613</v>
+      </c>
+      <c r="H99" s="74" t="s">
+        <v>1614</v>
+      </c>
+      <c r="I99" s="74" t="s">
+        <v>1615</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" ht="28">
+      <c r="A100" s="62"/>
+      <c r="B100" s="62"/>
+      <c r="C100" s="49" t="s">
+        <v>1564</v>
+      </c>
+      <c r="D100" s="62" t="s">
+        <v>1616</v>
+      </c>
+      <c r="E100" s="74" t="s">
+        <v>1618</v>
+      </c>
+      <c r="F100" s="74" t="s">
+        <v>1618</v>
+      </c>
+      <c r="G100" s="74" t="s">
+        <v>1619</v>
+      </c>
+      <c r="H100" s="74" t="s">
+        <v>1620</v>
+      </c>
+      <c r="I100" s="74" t="s">
+        <v>1621</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" ht="14">
+      <c r="A101" s="62"/>
+      <c r="B101" s="62"/>
+      <c r="C101" s="62" t="s">
+        <v>1565</v>
+      </c>
+      <c r="D101" s="62" t="s">
+        <v>1622</v>
+      </c>
+      <c r="E101" s="75" t="s">
+        <v>1626</v>
+      </c>
+      <c r="F101" s="75" t="s">
+        <v>1626</v>
+      </c>
+      <c r="G101" s="74" t="s">
+        <v>1627</v>
+      </c>
+      <c r="H101" s="74" t="s">
+        <v>1628</v>
+      </c>
+      <c r="I101" s="74" t="s">
+        <v>1629</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" ht="13">
       <c r="A102" s="16"/>
       <c r="B102" s="16"/>
       <c r="C102" s="16"/>
       <c r="D102" s="16"/>
-    </row>
-    <row r="103" spans="1:4" ht="13">
+      <c r="E102" s="52"/>
+    </row>
+    <row r="103" spans="1:9" ht="13">
       <c r="A103" s="16"/>
       <c r="B103" s="16"/>
       <c r="C103" s="16"/>
       <c r="D103" s="16"/>
-    </row>
-    <row r="104" spans="1:4" ht="13">
+      <c r="E103" s="52"/>
+    </row>
+    <row r="104" spans="1:9" ht="13">
       <c r="A104" s="16"/>
       <c r="B104" s="16"/>
       <c r="C104" s="16"/>
       <c r="D104" s="16"/>
-    </row>
-    <row r="105" spans="1:4" ht="13">
+      <c r="E104" s="52"/>
+    </row>
+    <row r="105" spans="1:9" ht="13">
       <c r="A105" s="16"/>
       <c r="B105" s="16"/>
       <c r="C105" s="16"/>
       <c r="D105" s="16"/>
-    </row>
-    <row r="106" spans="1:4" ht="13">
+      <c r="E105" s="52"/>
+    </row>
+    <row r="106" spans="1:9" ht="13">
       <c r="A106" s="16"/>
       <c r="B106" s="16"/>
       <c r="C106" s="16"/>
       <c r="D106" s="16"/>
-    </row>
-    <row r="107" spans="1:4" ht="13">
+      <c r="E106" s="52"/>
+    </row>
+    <row r="107" spans="1:9" ht="13">
       <c r="A107" s="16"/>
       <c r="B107" s="16"/>
       <c r="C107" s="16"/>
       <c r="D107" s="16"/>
-    </row>
-    <row r="108" spans="1:4" ht="13">
+      <c r="E107" s="52"/>
+    </row>
+    <row r="108" spans="1:9" ht="13">
       <c r="A108" s="16"/>
       <c r="B108" s="16"/>
       <c r="C108" s="16"/>
       <c r="D108" s="16"/>
-    </row>
-    <row r="109" spans="1:4" ht="13">
+      <c r="E108" s="52"/>
+    </row>
+    <row r="109" spans="1:9" ht="13">
       <c r="A109" s="16"/>
       <c r="B109" s="16"/>
       <c r="C109" s="16"/>
       <c r="D109" s="16"/>
-    </row>
-    <row r="110" spans="1:4" ht="13">
+      <c r="E109" s="52"/>
+    </row>
+    <row r="110" spans="1:9" ht="13">
       <c r="A110" s="16"/>
       <c r="B110" s="16"/>
       <c r="C110" s="16"/>
       <c r="D110" s="16"/>
-    </row>
-    <row r="111" spans="1:4" ht="13">
+      <c r="E110" s="52"/>
+    </row>
+    <row r="111" spans="1:9" ht="13">
       <c r="A111" s="16"/>
       <c r="B111" s="16"/>
       <c r="C111" s="16"/>
       <c r="D111" s="16"/>
-    </row>
-    <row r="112" spans="1:4" ht="13">
+      <c r="E111" s="52"/>
+    </row>
+    <row r="112" spans="1:9" ht="13">
       <c r="A112" s="16"/>
       <c r="B112" s="16"/>
       <c r="C112" s="16"/>
       <c r="D112" s="16"/>
-    </row>
-    <row r="113" spans="1:4" ht="13">
+      <c r="E112" s="52"/>
+    </row>
+    <row r="113" spans="1:5" ht="13">
       <c r="A113" s="16"/>
       <c r="B113" s="16"/>
       <c r="C113" s="16"/>
       <c r="D113" s="16"/>
-    </row>
-    <row r="114" spans="1:4" ht="13">
+      <c r="E113" s="74"/>
+    </row>
+    <row r="114" spans="1:5" ht="13">
       <c r="A114" s="16"/>
       <c r="B114" s="16"/>
       <c r="C114" s="16"/>
       <c r="D114" s="16"/>
-    </row>
-    <row r="115" spans="1:4" ht="13">
+      <c r="E114" s="52"/>
+    </row>
+    <row r="115" spans="1:5" ht="13">
       <c r="A115" s="16"/>
       <c r="B115" s="16"/>
       <c r="C115" s="16"/>
       <c r="D115" s="16"/>
-    </row>
-    <row r="116" spans="1:4" ht="13">
+      <c r="E115" s="74"/>
+    </row>
+    <row r="116" spans="1:5" ht="13">
       <c r="A116" s="16"/>
       <c r="B116" s="16"/>
       <c r="C116" s="16"/>
       <c r="D116" s="16"/>
-    </row>
-    <row r="117" spans="1:4" ht="13">
+      <c r="E116" s="62"/>
+    </row>
+    <row r="117" spans="1:5" ht="13">
       <c r="A117" s="16"/>
       <c r="B117" s="16"/>
       <c r="C117" s="16"/>
       <c r="D117" s="16"/>
-    </row>
-    <row r="118" spans="1:4" ht="13">
+      <c r="E117" s="74"/>
+    </row>
+    <row r="118" spans="1:5" ht="13">
       <c r="A118" s="16"/>
       <c r="B118" s="16"/>
       <c r="C118" s="16"/>
       <c r="D118" s="16"/>
-    </row>
-    <row r="119" spans="1:4" ht="13">
+      <c r="E118" s="62"/>
+    </row>
+    <row r="119" spans="1:5" ht="13">
       <c r="A119" s="16"/>
       <c r="B119" s="16"/>
       <c r="C119" s="16"/>
       <c r="D119" s="16"/>
-    </row>
-    <row r="120" spans="1:4" ht="13">
+      <c r="E119" s="74"/>
+    </row>
+    <row r="120" spans="1:5" ht="13">
       <c r="A120" s="16"/>
       <c r="B120" s="16"/>
       <c r="C120" s="16"/>
       <c r="D120" s="16"/>
-    </row>
-    <row r="121" spans="1:4" ht="13">
+      <c r="E120" s="74"/>
+    </row>
+    <row r="121" spans="1:5" ht="13">
       <c r="A121" s="16"/>
       <c r="B121" s="16"/>
       <c r="C121" s="16"/>
       <c r="D121" s="16"/>
-    </row>
-    <row r="122" spans="1:4" ht="13">
+      <c r="E121" s="74"/>
+    </row>
+    <row r="122" spans="1:5" ht="13">
       <c r="A122" s="16"/>
       <c r="B122" s="16"/>
       <c r="C122" s="16"/>
       <c r="D122" s="16"/>
-    </row>
-    <row r="123" spans="1:4" ht="13">
+      <c r="E122" s="75"/>
+    </row>
+    <row r="123" spans="1:5" ht="13">
       <c r="A123" s="16"/>
       <c r="B123" s="16"/>
       <c r="C123" s="16"/>
       <c r="D123" s="16"/>
     </row>
-    <row r="124" spans="1:4" ht="13">
+    <row r="124" spans="1:5" ht="13">
       <c r="A124" s="16"/>
       <c r="B124" s="16"/>
       <c r="C124" s="16"/>
       <c r="D124" s="16"/>
     </row>
-    <row r="125" spans="1:4" ht="13">
+    <row r="125" spans="1:5" ht="13">
       <c r="A125" s="16"/>
       <c r="B125" s="16"/>
       <c r="C125" s="16"/>
       <c r="D125" s="16"/>
     </row>
-    <row r="126" spans="1:4" ht="13">
+    <row r="126" spans="1:5" ht="13">
       <c r="A126" s="16"/>
       <c r="B126" s="16"/>
       <c r="C126" s="16"/>
       <c r="D126" s="16"/>
     </row>
-    <row r="127" spans="1:4" ht="13">
+    <row r="127" spans="1:5" ht="13">
       <c r="A127" s="16"/>
       <c r="B127" s="16"/>
       <c r="C127" s="16"/>
       <c r="D127" s="16"/>
     </row>
-    <row r="128" spans="1:4" ht="13">
+    <row r="128" spans="1:5" ht="13">
       <c r="A128" s="16"/>
       <c r="B128" s="16"/>
       <c r="C128" s="16"/>
@@ -18909,9 +19241,6 @@
       <c r="D49" s="49" t="s">
         <v>242</v>
       </c>
-      <c r="E49" s="51" t="s">
-        <v>448</v>
-      </c>
       <c r="F49" s="52" t="s">
         <v>243</v>
       </c>
@@ -18935,9 +19264,6 @@
       </c>
       <c r="D50" s="49" t="s">
         <v>25</v>
-      </c>
-      <c r="E50" s="51" t="s">
-        <v>421</v>
       </c>
       <c r="F50" s="52" t="s">
         <v>25</v>
@@ -18961,9 +19287,6 @@
       <c r="D51" s="49" t="s">
         <v>252</v>
       </c>
-      <c r="E51" s="51" t="s">
-        <v>449</v>
-      </c>
       <c r="F51" s="52" t="s">
         <v>253</v>
       </c>
@@ -18988,9 +19311,6 @@
       <c r="D52" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="E52" s="51" t="s">
-        <v>448</v>
-      </c>
       <c r="F52" s="9" t="s">
         <v>683</v>
       </c>
@@ -19014,9 +19334,6 @@
       </c>
       <c r="D53" s="6" t="s">
         <v>687</v>
-      </c>
-      <c r="E53" s="76" t="s">
-        <v>1649</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>688</v>
@@ -19040,9 +19357,6 @@
       <c r="D54" s="16" t="s">
         <v>693</v>
       </c>
-      <c r="E54" s="76" t="s">
-        <v>1650</v>
-      </c>
       <c r="F54" s="9" t="s">
         <v>694</v>
       </c>
@@ -19067,9 +19381,6 @@
       <c r="D55" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="E55" s="51" t="s">
-        <v>448</v>
-      </c>
       <c r="F55" s="9" t="s">
         <v>683</v>
       </c>
@@ -19093,9 +19404,6 @@
       </c>
       <c r="D56" s="6" t="s">
         <v>1039</v>
-      </c>
-      <c r="E56" s="76" t="s">
-        <v>1651</v>
       </c>
       <c r="F56" s="9" t="s">
         <v>1040</v>
@@ -19119,9 +19427,6 @@
       <c r="D57" s="6" t="s">
         <v>1045</v>
       </c>
-      <c r="E57" s="76" t="s">
-        <v>1652</v>
-      </c>
       <c r="F57" s="9" t="s">
         <v>1046</v>
       </c>
@@ -19146,9 +19451,6 @@
       <c r="D58" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="E58" s="51" t="s">
-        <v>448</v>
-      </c>
       <c r="F58" s="9" t="s">
         <v>1391</v>
       </c>
@@ -19172,9 +19474,6 @@
       </c>
       <c r="D59" s="6" t="s">
         <v>1394</v>
-      </c>
-      <c r="E59" s="76" t="s">
-        <v>1653</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>1395</v>
@@ -19198,9 +19497,6 @@
       <c r="D60" s="6" t="s">
         <v>1399</v>
       </c>
-      <c r="E60" s="76" t="s">
-        <v>1654</v>
-      </c>
       <c r="F60" s="9" t="s">
         <v>1400</v>
       </c>
@@ -19905,9 +20201,6 @@
       <c r="D91" s="62" t="s">
         <v>1566</v>
       </c>
-      <c r="E91" s="73" t="s">
-        <v>1568</v>
-      </c>
       <c r="F91" s="52" t="s">
         <v>1570</v>
       </c>
@@ -19930,9 +20223,6 @@
       <c r="D92" s="62" t="s">
         <v>1567</v>
       </c>
-      <c r="E92" s="74" t="s">
-        <v>1569</v>
-      </c>
       <c r="F92" s="74" t="s">
         <v>1571</v>
       </c>
@@ -19955,9 +20245,6 @@
       <c r="D93" s="62" t="s">
         <v>1588</v>
       </c>
-      <c r="E93" s="73" t="s">
-        <v>1578</v>
-      </c>
       <c r="F93" s="52" t="s">
         <v>1580</v>
       </c>
@@ -19980,9 +20267,6 @@
       <c r="D94" s="62" t="s">
         <v>1587</v>
       </c>
-      <c r="E94" s="74" t="s">
-        <v>1579</v>
-      </c>
       <c r="F94" s="74" t="s">
         <v>1581</v>
       </c>
@@ -20005,9 +20289,6 @@
       <c r="D95" s="62" t="s">
         <v>1589</v>
       </c>
-      <c r="E95" s="75" t="s">
-        <v>1591</v>
-      </c>
       <c r="F95" s="62" t="s">
         <v>1592</v>
       </c>
@@ -20029,9 +20310,6 @@
       </c>
       <c r="D96" s="62" t="s">
         <v>1590</v>
-      </c>
-      <c r="E96" s="74" t="s">
-        <v>1600</v>
       </c>
       <c r="F96" s="74" t="s">
         <v>1599</v>
